--- a/jogos_2025-10-19.xlsx
+++ b/jogos_2025-10-19.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK272"/>
+  <dimension ref="A1:AK273"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Porreres</t>
+          <t>Girona II</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2052,22 +2052,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Porreres</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Deportivo Alaves II</t>
+          <t>Ourense CF</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gernika Club</t>
+          <t>Real Madrid II</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2310,22 +2310,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Girona II</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Deportivo de La Coruña W</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Atletico Madrid W</t>
+          <t>CD Alcoyano</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>SD Ponferradina</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Xerez CD</t>
+          <t>Zamora CF</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Linares Deportivo</t>
+          <t>Gimnàstic de Tarragona</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>CF Lorca Deportiva</t>
+          <t>SD Tarazona</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>Monção</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>CDA Navalcarnero</t>
+          <t>Ribeira Brava</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>Deportivo Alaves II</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>Gernika Club</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>UD Socuéllamos</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Real Sociedad W</t>
+          <t>Rayo Majadahonda</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,13 +3249,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3288,10 +3288,10 @@
         <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AA22" t="n">
         <v>0</v>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>CD Alcoyano</t>
+          <t>La Unión Atlético</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Monção</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ribeira Brava</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Ibiza Islas Pitiusas</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Valencia II</t>
+          <t>Xerez CD</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>Linares Deportivo</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>La Unión Atlético</t>
+          <t>CF Lorca Deportiva</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3858,22 +3858,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>CDA Navalcarnero</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,13 +4023,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4062,10 +4062,10 @@
         <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AA28" t="n">
         <v>0</v>
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Almería II</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>UCAM Murcia CF</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4245,22 +4245,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Ourense CF</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Real Madrid II</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Puente Genil</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Real Jaén CF</t>
+          <t>Real Sociedad W</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Gimnàstic de Tarragona</t>
+          <t>Deportivo de La Coruña W</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>SD Tarazona</t>
+          <t>Atletico Madrid W</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>UD Socuéllamos</t>
+          <t>Ibiza Islas Pitiusas</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rayo Majadahonda</t>
+          <t>Valencia II</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>SD Ponferradina</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Zamora CF</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Almería II</t>
+          <t>Puente Genil</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>UCAM Murcia CF</t>
+          <t>Real Jaén CF</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Telstar</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Heerenveen</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>3</v>
+        <v>2.13</v>
       </c>
       <c r="M36" t="n">
-        <v>3.75</v>
+        <v>3.45</v>
       </c>
       <c r="N36" t="n">
-        <v>2.25</v>
+        <v>3.4</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5094,10 +5094,10 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.75</v>
+        <v>1.9</v>
       </c>
       <c r="Z36" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="AA36" t="n">
         <v>0</v>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Telstar</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,13 +5184,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.13</v>
+        <v>3</v>
       </c>
       <c r="M37" t="n">
-        <v>3.45</v>
+        <v>3.75</v>
       </c>
       <c r="N37" t="n">
-        <v>3.4</v>
+        <v>2.25</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5223,10 +5223,10 @@
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.9</v>
+        <v>1.75</v>
       </c>
       <c r="Z37" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="AA37" t="n">
         <v>0</v>
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,13 +5313,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5352,10 +5352,10 @@
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="Z38" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AA38" t="n">
         <v>0</v>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,13 +5700,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5739,10 +5739,10 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Z41" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA41" t="n">
         <v>0</v>
@@ -5793,7 +5793,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Budafoki MTE</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,13 +5829,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5868,16 +5868,16 @@
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z42" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AA42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -5922,22 +5922,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Hai Phong</t>
+          <t>Utsikten</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Hoang Anh Gia Lai</t>
+          <t>Trelleborg</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,13 +5958,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5997,10 +5997,10 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z43" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA43" t="n">
         <v>0</v>
@@ -6051,7 +6051,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Csákvári TK</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6180,22 +6180,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Utsikten</t>
+          <t>Hai Phong</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Trelleborg</t>
+          <t>Hoang Anh Gia Lai</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6309,22 +6309,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Pho Hien</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>FLC Thanh Hoa</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6438,7 +6438,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Rayong</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Prachuap</t>
+          <t>Budafoki MTE</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6567,22 +6567,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Rayong</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Prachuap</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6603,13 +6603,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="M48" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6642,10 +6642,10 @@
         <v>0</v>
       </c>
       <c r="Y48" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z48" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA48" t="n">
         <v>0</v>
@@ -6696,7 +6696,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>Karcag SE</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>Csákvári TK</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Pho Hien</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>FLC Thanh Hoa</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6861,13 +6861,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="N50" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6900,16 +6900,16 @@
         <v>0</v>
       </c>
       <c r="Y50" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Z50" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
@@ -7083,7 +7083,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Ulm</t>
+          <t>Cercle Brugge</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7119,13 +7119,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>2.4</v>
+        <v>3.2</v>
       </c>
       <c r="M52" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="N52" t="n">
-        <v>2.55</v>
+        <v>2.12</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -7158,10 +7158,10 @@
         <v>0</v>
       </c>
       <c r="Y52" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z52" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA52" t="n">
         <v>0</v>
@@ -7212,7 +7212,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Chonburi</t>
+          <t>FK Sochi</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Chiangrai United</t>
+          <t>Zenit</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7248,13 +7248,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="M53" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -7287,10 +7287,10 @@
         <v>0</v>
       </c>
       <c r="Y53" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Z53" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA53" t="n">
         <v>0</v>
@@ -7341,7 +7341,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Cercle Brugge</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7377,13 +7377,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>3.2</v>
+        <v>1.65</v>
       </c>
       <c r="M54" t="n">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="N54" t="n">
-        <v>2.12</v>
+        <v>4.7</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -7416,16 +7416,16 @@
         <v>0</v>
       </c>
       <c r="Y54" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="Z54" t="n">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="AA54" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB54" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC54" t="n">
         <v>0</v>
@@ -7470,22 +7470,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Tampines Rovers</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Balestier Khalsa</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7506,13 +7506,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M55" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N55" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7545,10 +7545,10 @@
         <v>0</v>
       </c>
       <c r="Y55" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Z55" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AA55" t="n">
         <v>0</v>
@@ -7599,7 +7599,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Chonburi</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Magdeburg</t>
+          <t>Chiangrai United</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7635,13 +7635,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="M56" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="N56" t="n">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7674,16 +7674,16 @@
         <v>0</v>
       </c>
       <c r="Y56" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z56" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AA56" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AB56" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC56" t="n">
         <v>0</v>
@@ -7728,22 +7728,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7764,13 +7764,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N57" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7803,16 +7803,16 @@
         <v>0</v>
       </c>
       <c r="Y57" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z57" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AA57" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB57" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC57" t="n">
         <v>0</v>
@@ -7857,22 +7857,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N58" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7932,10 +7932,10 @@
         <v>0</v>
       </c>
       <c r="Y58" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Z58" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AA58" t="n">
         <v>0</v>
@@ -7986,7 +7986,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Ulm</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8022,13 +8022,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M59" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N59" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Nantong Zhiyun</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Guangxi Baoyun</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8244,7 +8244,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8254,12 +8254,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Nantong Zhiyun</t>
+          <t>Tampines Rovers</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Guangxi Baoyun</t>
+          <t>Balestier Khalsa</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8373,22 +8373,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8502,7 +8502,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>FK Sochi</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Zenit</t>
+          <t>Magdeburg</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8538,14 +8538,14 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>10.5</v>
+        <v>1.83</v>
       </c>
       <c r="M63" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="N63" t="n">
         <v>4.7</v>
       </c>
-      <c r="N63" t="n">
-        <v>1.35</v>
-      </c>
       <c r="O63" t="n">
         <v>0</v>
       </c>
@@ -8577,16 +8577,16 @@
         <v>0</v>
       </c>
       <c r="Y63" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Z63" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AA63" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AB63" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC63" t="n">
         <v>0</v>
@@ -8889,22 +8889,22 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Metta - LU</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -9018,7 +9018,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -9028,12 +9028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Kanchanaburi</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Uthai Thani</t>
+          <t>Pelister</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9157,12 +9157,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9276,22 +9276,22 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9312,13 +9312,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="N69" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -9351,10 +9351,10 @@
         <v>0</v>
       </c>
       <c r="Y69" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z69" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AA69" t="n">
         <v>0</v>
@@ -9405,7 +9405,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9441,13 +9441,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M70" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N70" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -9480,10 +9480,10 @@
         <v>0</v>
       </c>
       <c r="Y70" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z70" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA70" t="n">
         <v>0</v>
@@ -9534,22 +9534,22 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9570,13 +9570,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>2.2</v>
+        <v>1.48</v>
       </c>
       <c r="M71" t="n">
-        <v>3.5</v>
+        <v>3.83</v>
       </c>
       <c r="N71" t="n">
-        <v>3.2</v>
+        <v>6.76</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -9609,10 +9609,10 @@
         <v>0</v>
       </c>
       <c r="Y71" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="Z71" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="AA71" t="n">
         <v>0</v>
@@ -9663,7 +9663,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -9673,12 +9673,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9699,13 +9699,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N72" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9738,10 +9738,10 @@
         <v>0</v>
       </c>
       <c r="Y72" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z72" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA72" t="n">
         <v>0</v>
@@ -9792,7 +9792,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9802,12 +9802,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Kanchanaburi</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Uthai Thani</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9828,13 +9828,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="M73" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N73" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9921,7 +9921,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9931,12 +9931,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Pelister</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9957,13 +9957,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="M74" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="N74" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -10050,7 +10050,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10179,22 +10179,22 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10215,13 +10215,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>2.13</v>
+        <v>1.58</v>
       </c>
       <c r="M76" t="n">
-        <v>3.7</v>
+        <v>4.05</v>
       </c>
       <c r="N76" t="n">
-        <v>3.2</v>
+        <v>5.8</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -10254,10 +10254,10 @@
         <v>0</v>
       </c>
       <c r="Y76" t="n">
-        <v>1.65</v>
+        <v>1.95</v>
       </c>
       <c r="Z76" t="n">
-        <v>2.25</v>
+        <v>1.85</v>
       </c>
       <c r="AA76" t="n">
         <v>0</v>
@@ -10308,7 +10308,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -10318,12 +10318,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10437,7 +10437,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -10447,12 +10447,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10566,22 +10566,22 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10602,13 +10602,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="M79" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N79" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -10641,10 +10641,10 @@
         <v>0</v>
       </c>
       <c r="Y79" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z79" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA79" t="n">
         <v>0</v>
@@ -10695,22 +10695,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Metta - LU</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10731,13 +10731,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="M80" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N80" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -10770,10 +10770,10 @@
         <v>0</v>
       </c>
       <c r="Y80" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z80" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA80" t="n">
         <v>0</v>
@@ -10834,12 +10834,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Piteå Women</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10953,22 +10953,22 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>CSKA Sofia</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10989,13 +10989,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>6.4</v>
+        <v>2.2</v>
       </c>
       <c r="M82" t="n">
         <v>3.5</v>
       </c>
       <c r="N82" t="n">
-        <v>1.52</v>
+        <v>3.2</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -11028,10 +11028,10 @@
         <v>0</v>
       </c>
       <c r="Y82" t="n">
-        <v>2.08</v>
+        <v>1.8</v>
       </c>
       <c r="Z82" t="n">
-        <v>1.64</v>
+        <v>2</v>
       </c>
       <c r="AA82" t="n">
         <v>0</v>
@@ -11082,22 +11082,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11118,13 +11118,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>2.02</v>
+        <v>2.95</v>
       </c>
       <c r="M83" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="N83" t="n">
-        <v>3.55</v>
+        <v>2.11</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -11157,10 +11157,10 @@
         <v>0</v>
       </c>
       <c r="Y83" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z83" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AA83" t="n">
         <v>0</v>
@@ -11211,7 +11211,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -11221,12 +11221,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11340,7 +11340,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -11350,12 +11350,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>CSKA Sofia</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11376,13 +11376,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="M85" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N85" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -11415,10 +11415,10 @@
         <v>0</v>
       </c>
       <c r="Y85" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Z85" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AA85" t="n">
         <v>0</v>
@@ -11727,7 +11727,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -11737,12 +11737,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Excelsior</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -11763,13 +11763,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="M88" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N88" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -11802,16 +11802,16 @@
         <v>0</v>
       </c>
       <c r="Y88" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z88" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA88" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AB88" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC88" t="n">
         <v>0</v>
@@ -11985,7 +11985,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11995,12 +11995,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12114,7 +12114,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Groningen</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Sparta Rotterdam</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12150,13 +12150,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M91" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N91" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -12189,16 +12189,16 @@
         <v>0</v>
       </c>
       <c r="Y91" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Z91" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA91" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="AB91" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC91" t="n">
         <v>0</v>
@@ -12243,22 +12243,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Skeid</t>
+          <t>Blau-Weiß Linz</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12279,13 +12279,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="M92" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N92" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -12318,10 +12318,10 @@
         <v>0</v>
       </c>
       <c r="Y92" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z92" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA92" t="n">
         <v>0</v>
@@ -12372,7 +12372,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -12382,12 +12382,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Excelsior</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12408,13 +12408,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="M93" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N93" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -12447,16 +12447,16 @@
         <v>0</v>
       </c>
       <c r="Y93" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z93" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA93" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="AB93" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC93" t="n">
         <v>0</v>
@@ -12501,7 +12501,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -12511,12 +12511,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Salzburg</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Rheindorf Altach</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12537,13 +12537,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="M94" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="N94" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -12576,10 +12576,10 @@
         <v>0</v>
       </c>
       <c r="Y94" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Z94" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AA94" t="n">
         <v>0</v>
@@ -12640,12 +12640,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -12759,22 +12759,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Skeid</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -12888,7 +12888,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -12898,12 +12898,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Blau-Weiß Linz</t>
+          <t>Groningen</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Sparta Rotterdam</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -12924,13 +12924,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>4.9</v>
+        <v>1.95</v>
       </c>
       <c r="M97" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="N97" t="n">
-        <v>1.73</v>
+        <v>3.8</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12963,16 +12963,16 @@
         <v>0</v>
       </c>
       <c r="Y97" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="Z97" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AA97" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AB97" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC97" t="n">
         <v>0</v>
@@ -13017,7 +13017,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -13027,12 +13027,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Salzburg</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Rheindorf Altach</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13053,13 +13053,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="M98" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="N98" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -13092,10 +13092,10 @@
         <v>0</v>
       </c>
       <c r="Y98" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Z98" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA98" t="n">
         <v>0</v>
@@ -13404,22 +13404,22 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>76 Iğdır Belediyespor</t>
+          <t>Ilves</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>Inter Turku</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13533,7 +13533,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -13543,12 +13543,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13569,13 +13569,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>2.1</v>
+        <v>1.87</v>
       </c>
       <c r="M102" t="n">
-        <v>3.2</v>
+        <v>3.85</v>
       </c>
       <c r="N102" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -13608,10 +13608,10 @@
         <v>0</v>
       </c>
       <c r="Y102" t="n">
-        <v>2.35</v>
+        <v>1.68</v>
       </c>
       <c r="Z102" t="n">
-        <v>1.6</v>
+        <v>2.2</v>
       </c>
       <c r="AA102" t="n">
         <v>0</v>
@@ -13662,7 +13662,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -13672,12 +13672,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Gnistan</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Okzhetpes</t>
+          <t>SJK</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -13698,13 +13698,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="M103" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="N103" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -13743,10 +13743,10 @@
         <v>0</v>
       </c>
       <c r="AA103" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB103" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC103" t="n">
         <v>0</v>
@@ -13791,7 +13791,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -13801,12 +13801,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -13827,13 +13827,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>3.25</v>
+        <v>2.15</v>
       </c>
       <c r="M104" t="n">
-        <v>3.35</v>
+        <v>3.7</v>
       </c>
       <c r="N104" t="n">
-        <v>2.2</v>
+        <v>3.15</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -13866,10 +13866,10 @@
         <v>0</v>
       </c>
       <c r="Y104" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="Z104" t="n">
-        <v>1.65</v>
+        <v>2</v>
       </c>
       <c r="AA104" t="n">
         <v>0</v>
@@ -13920,22 +13920,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Umeå</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -13956,13 +13956,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>2.02</v>
+        <v>1.62</v>
       </c>
       <c r="M105" t="n">
-        <v>3.3</v>
+        <v>4.05</v>
       </c>
       <c r="N105" t="n">
-        <v>3.95</v>
+        <v>4.8</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -13995,10 +13995,10 @@
         <v>0</v>
       </c>
       <c r="Y105" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Z105" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AA105" t="n">
         <v>0</v>
@@ -14049,7 +14049,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -14059,12 +14059,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>76 Iğdır Belediyespor</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -14085,13 +14085,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="M106" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N106" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -14124,10 +14124,10 @@
         <v>0</v>
       </c>
       <c r="Y106" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z106" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA106" t="n">
         <v>0</v>
@@ -14178,22 +14178,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>SJK</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -14214,13 +14214,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>3.35</v>
+        <v>2.1</v>
       </c>
       <c r="M107" t="n">
-        <v>4.05</v>
+        <v>3.2</v>
       </c>
       <c r="N107" t="n">
-        <v>1.97</v>
+        <v>3.8</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -14253,16 +14253,16 @@
         <v>0</v>
       </c>
       <c r="Y107" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Z107" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AA107" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB107" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC107" t="n">
         <v>0</v>
@@ -14307,22 +14307,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Ilves</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Inter Turku</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -14343,13 +14343,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="M108" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N108" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -14382,10 +14382,10 @@
         <v>0</v>
       </c>
       <c r="Y108" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z108" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA108" t="n">
         <v>0</v>
@@ -14436,22 +14436,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -14472,13 +14472,13 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="M109" t="n">
-        <v>3.85</v>
+        <v>3.48</v>
       </c>
       <c r="N109" t="n">
-        <v>3.9</v>
+        <v>3.22</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
@@ -14511,10 +14511,10 @@
         <v>0</v>
       </c>
       <c r="Y109" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Z109" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA109" t="n">
         <v>0</v>
@@ -14565,22 +14565,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -14601,13 +14601,13 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="M110" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N110" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -14640,10 +14640,10 @@
         <v>0</v>
       </c>
       <c r="Y110" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z110" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA110" t="n">
         <v>0</v>
@@ -14694,22 +14694,22 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -14730,13 +14730,13 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M111" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N111" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="O111" t="n">
         <v>0</v>
@@ -14769,10 +14769,10 @@
         <v>0</v>
       </c>
       <c r="Y111" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z111" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AA111" t="n">
         <v>0</v>
@@ -14823,22 +14823,22 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -14859,13 +14859,13 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M112" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N112" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O112" t="n">
         <v>0</v>
@@ -14898,10 +14898,10 @@
         <v>0</v>
       </c>
       <c r="Y112" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z112" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA112" t="n">
         <v>0</v>
@@ -14962,12 +14962,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>Okzhetpes</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -15091,12 +15091,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Umeå</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -15117,13 +15117,13 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="M114" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="N114" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="O114" t="n">
         <v>0</v>
@@ -15339,7 +15339,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -15349,12 +15349,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Zalaegerszegi TE</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Puskás</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -15468,7 +15468,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -15478,12 +15478,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -15597,7 +15597,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -15607,12 +15607,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Zalaegerszegi TE</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Puskás</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -15855,7 +15855,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -15984,22 +15984,22 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -16123,12 +16123,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -16371,7 +16371,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -16381,12 +16381,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Atert Bissen</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>UN Käerjéng</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -16500,7 +16500,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -16510,12 +16510,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>Rubin Kazan</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Baltika</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -16536,13 +16536,13 @@
         </is>
       </c>
       <c r="L125" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M125" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N125" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O125" t="n">
         <v>0</v>
@@ -16575,10 +16575,10 @@
         <v>0</v>
       </c>
       <c r="Y125" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Z125" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AA125" t="n">
         <v>0</v>
@@ -16629,22 +16629,22 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -16758,7 +16758,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -16768,12 +16768,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>FCV Dender EH</t>
+          <t>Hostert</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>F91 Dudelange</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -16794,13 +16794,13 @@
         </is>
       </c>
       <c r="L127" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="M127" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N127" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="O127" t="n">
         <v>0</v>
@@ -16833,10 +16833,10 @@
         <v>0</v>
       </c>
       <c r="Y127" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z127" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AA127" t="n">
         <v>0</v>
@@ -16897,12 +16897,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Afturelding</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>Vestri</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -17016,7 +17016,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -17026,12 +17026,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Afturelding</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Vestri</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -17145,22 +17145,22 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -17274,22 +17274,22 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>Jeunesse Canach</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Victoria Rosport</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -17403,7 +17403,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -17413,12 +17413,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Atert Bissen</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>UN Käerjéng</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -17532,22 +17532,22 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Mamer</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Progrès Niederkorn</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -17661,7 +17661,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -17671,12 +17671,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Differdange 03</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Swift Hesperange</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -17790,7 +17790,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -17800,12 +17800,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -17919,22 +17919,22 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Rodange</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>UT Pétange</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -18048,7 +18048,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -18058,12 +18058,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Rayo Vallecano II</t>
+          <t>Real Avilés</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Colonia Moscardó</t>
+          <t>Talavera CF</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -18177,7 +18177,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -18187,12 +18187,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Mamer</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>Progrès Niederkorn</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -18306,7 +18306,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -18316,12 +18316,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>FCV Dender EH</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -18342,13 +18342,13 @@
         </is>
       </c>
       <c r="L139" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="M139" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N139" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O139" t="n">
         <v>0</v>
@@ -18381,10 +18381,10 @@
         <v>0</v>
       </c>
       <c r="Y139" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z139" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA139" t="n">
         <v>0</v>
@@ -18435,7 +18435,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -18445,12 +18445,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -18564,22 +18564,22 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -18693,7 +18693,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -18703,12 +18703,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Differdange 03</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Hajduk Split</t>
+          <t>Swift Hesperange</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -18822,7 +18822,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -18832,12 +18832,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Gazişehir Gaziantep</t>
+          <t>Rodange</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>UT Pétange</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -18951,7 +18951,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -18961,12 +18961,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Rubin Kazan</t>
+          <t>Gazişehir Gaziantep</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Baltika</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -18987,13 +18987,13 @@
         </is>
       </c>
       <c r="L144" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M144" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N144" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O144" t="n">
         <v>0</v>
@@ -19026,10 +19026,10 @@
         <v>0</v>
       </c>
       <c r="Y144" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Z144" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AA144" t="n">
         <v>0</v>
@@ -19080,7 +19080,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -19090,12 +19090,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -19209,7 +19209,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -19219,12 +19219,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Jeunesse d'Esch</t>
+          <t>Rayo Vallecano II</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Mondorf-les-Bains</t>
+          <t>Colonia Moscardó</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -19348,12 +19348,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Hostert</t>
+          <t>Jeunesse d'Esch</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>F91 Dudelange</t>
+          <t>Mondorf-les-Bains</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -19467,22 +19467,22 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Jeunesse Canach</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Victoria Rosport</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -19596,7 +19596,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -19606,12 +19606,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Real Avilés</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Talavera CF</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -19735,12 +19735,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -19854,7 +19854,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -19864,12 +19864,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -19983,7 +19983,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -19993,12 +19993,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -20112,7 +20112,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -20122,12 +20122,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Cherno More</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Lausanne Sport</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -20148,13 +20148,13 @@
         </is>
       </c>
       <c r="L153" t="n">
-        <v>3.69</v>
+        <v>2.35</v>
       </c>
       <c r="M153" t="n">
-        <v>3.01</v>
+        <v>3.65</v>
       </c>
       <c r="N153" t="n">
-        <v>2.11</v>
+        <v>2.85</v>
       </c>
       <c r="O153" t="n">
         <v>0</v>
@@ -20187,10 +20187,10 @@
         <v>0</v>
       </c>
       <c r="Y153" t="n">
-        <v>2.5</v>
+        <v>1.6</v>
       </c>
       <c r="Z153" t="n">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="AA153" t="n">
         <v>0</v>
@@ -20241,7 +20241,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -20251,12 +20251,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -20280,10 +20280,10 @@
         <v>1.75</v>
       </c>
       <c r="M154" t="n">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="N154" t="n">
-        <v>5.1</v>
+        <v>4.05</v>
       </c>
       <c r="O154" t="n">
         <v>0</v>
@@ -20316,16 +20316,16 @@
         <v>0</v>
       </c>
       <c r="Y154" t="n">
-        <v>1.9</v>
+        <v>1.44</v>
       </c>
       <c r="Z154" t="n">
-        <v>1.9</v>
+        <v>2.6</v>
       </c>
       <c r="AA154" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB154" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC154" t="n">
         <v>0</v>
@@ -20370,7 +20370,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -20380,12 +20380,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -20406,13 +20406,13 @@
         </is>
       </c>
       <c r="L155" t="n">
-        <v>2.11</v>
+        <v>1.75</v>
       </c>
       <c r="M155" t="n">
-        <v>3.05</v>
+        <v>3.5</v>
       </c>
       <c r="N155" t="n">
-        <v>3.66</v>
+        <v>5.1</v>
       </c>
       <c r="O155" t="n">
         <v>0</v>
@@ -20445,10 +20445,10 @@
         <v>0</v>
       </c>
       <c r="Y155" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Z155" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA155" t="n">
         <v>0</v>
@@ -20499,7 +20499,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -20509,12 +20509,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -20535,13 +20535,13 @@
         </is>
       </c>
       <c r="L156" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="M156" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N156" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="O156" t="n">
         <v>0</v>
@@ -20757,22 +20757,22 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>1860 München</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -20793,13 +20793,13 @@
         </is>
       </c>
       <c r="L158" t="n">
-        <v>2.45</v>
+        <v>1.68</v>
       </c>
       <c r="M158" t="n">
-        <v>3.54</v>
+        <v>4.3</v>
       </c>
       <c r="N158" t="n">
-        <v>2.52</v>
+        <v>4.4</v>
       </c>
       <c r="O158" t="n">
         <v>0</v>
@@ -20832,10 +20832,10 @@
         <v>0</v>
       </c>
       <c r="Y158" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z158" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA158" t="n">
         <v>0</v>
@@ -20886,7 +20886,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -20896,12 +20896,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Cherno More</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Lausanne Sport</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -20922,13 +20922,13 @@
         </is>
       </c>
       <c r="L159" t="n">
-        <v>2.35</v>
+        <v>3.69</v>
       </c>
       <c r="M159" t="n">
-        <v>3.65</v>
+        <v>3.01</v>
       </c>
       <c r="N159" t="n">
-        <v>2.85</v>
+        <v>2.11</v>
       </c>
       <c r="O159" t="n">
         <v>0</v>
@@ -20961,10 +20961,10 @@
         <v>0</v>
       </c>
       <c r="Y159" t="n">
-        <v>1.6</v>
+        <v>2.5</v>
       </c>
       <c r="Z159" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="AA159" t="n">
         <v>0</v>
@@ -21015,22 +21015,22 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>1860 München</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -21051,13 +21051,13 @@
         </is>
       </c>
       <c r="L160" t="n">
-        <v>1.68</v>
+        <v>2.45</v>
       </c>
       <c r="M160" t="n">
-        <v>4.3</v>
+        <v>3.54</v>
       </c>
       <c r="N160" t="n">
-        <v>4.4</v>
+        <v>2.52</v>
       </c>
       <c r="O160" t="n">
         <v>0</v>
@@ -21090,10 +21090,10 @@
         <v>0</v>
       </c>
       <c r="Y160" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z160" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA160" t="n">
         <v>0</v>
@@ -21144,7 +21144,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -21154,12 +21154,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -21180,13 +21180,13 @@
         </is>
       </c>
       <c r="L161" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="M161" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N161" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="O161" t="n">
         <v>0</v>
@@ -21225,10 +21225,10 @@
         <v>0</v>
       </c>
       <c r="AA161" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB161" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC161" t="n">
         <v>0</v>
@@ -21273,7 +21273,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -21283,12 +21283,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -21309,13 +21309,13 @@
         </is>
       </c>
       <c r="L162" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="M162" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="N162" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="O162" t="n">
         <v>0</v>
@@ -21348,16 +21348,16 @@
         <v>0</v>
       </c>
       <c r="Y162" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Z162" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AA162" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AB162" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AC162" t="n">
         <v>0</v>
@@ -21402,7 +21402,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -21412,12 +21412,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>CD Lealtad</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña II</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -21526,12 +21526,12 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -21541,12 +21541,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>CD Lealtad</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Deportivo La Coruña II</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -21567,13 +21567,13 @@
         </is>
       </c>
       <c r="L164" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="M164" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N164" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="O164" t="n">
         <v>0</v>
@@ -21606,10 +21606,10 @@
         <v>0</v>
       </c>
       <c r="Y164" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="Z164" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA164" t="n">
         <v>0</v>
@@ -21646,7 +21646,7 @@
         <v>0</v>
       </c>
       <c r="AK164" s="3" t="n">
-        <v>45949.5</v>
+        <v>45949.48958333334</v>
       </c>
     </row>
     <row r="165">
@@ -21660,7 +21660,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -21670,12 +21670,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>Szentlőrinc SE</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -21789,7 +21789,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -21799,12 +21799,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -21825,13 +21825,13 @@
         </is>
       </c>
       <c r="L166" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="M166" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N166" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="O166" t="n">
         <v>0</v>
@@ -21864,10 +21864,10 @@
         <v>0</v>
       </c>
       <c r="Y166" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="Z166" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA166" t="n">
         <v>0</v>
@@ -21918,7 +21918,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -21928,12 +21928,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Sarriana</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -22057,12 +22057,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>Kozármisleny</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -22176,7 +22176,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -22186,12 +22186,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>Beasain</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>Eibar II</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -22305,7 +22305,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -22315,12 +22315,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Union Estepona CF</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Yeclano Deportivo</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -22434,7 +22434,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -22444,12 +22444,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Quintanar del Rey</t>
+          <t>SD Ejea</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -22563,7 +22563,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -22573,12 +22573,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Bergantiños</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Burgos Promesas</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -22692,7 +22692,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -22702,12 +22702,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Szentlőrinc SE</t>
+          <t>Real Zaragoza II</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -22821,7 +22821,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -22831,12 +22831,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Rabotnički</t>
+          <t>Szeged 2011</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Makedonija GjP</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -22950,7 +22950,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -22960,12 +22960,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Kozármisleny</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Sestao River Club</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -23089,12 +23089,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>CD Ebro</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Sestao River Club</t>
+          <t>UD Mutilvera</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -23208,7 +23208,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -23218,12 +23218,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -23337,7 +23337,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -23347,12 +23347,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Szeged 2011</t>
+          <t>Sarriana</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -23466,7 +23466,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -23476,12 +23476,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>UD Granadilla Tenerife</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Levante Las Planas</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -23595,7 +23595,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -23605,12 +23605,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>CD Ebro</t>
+          <t>UD Granadilla Tenerife</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>UD Mutilvera</t>
+          <t>Levante Las Planas</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -23724,7 +23724,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -23734,12 +23734,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Beasain</t>
+          <t>Rapid Wien</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Eibar II</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -23760,13 +23760,13 @@
         </is>
       </c>
       <c r="L181" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M181" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N181" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O181" t="n">
         <v>0</v>
@@ -23799,10 +23799,10 @@
         <v>0</v>
       </c>
       <c r="Y181" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z181" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA181" t="n">
         <v>0</v>
@@ -23853,7 +23853,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -23863,12 +23863,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Real Zaragoza II</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -23982,7 +23982,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -23992,12 +23992,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>SD Ejea</t>
+          <t>Rabotnički</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -24111,7 +24111,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -24121,12 +24121,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -24240,7 +24240,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -24250,12 +24250,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Bergantiños</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Burgos Promesas</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -24369,7 +24369,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -24379,12 +24379,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Rapid Wien</t>
+          <t>Quintanar del Rey</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -24405,13 +24405,13 @@
         </is>
       </c>
       <c r="L186" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M186" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N186" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="O186" t="n">
         <v>0</v>
@@ -24444,10 +24444,10 @@
         <v>0</v>
       </c>
       <c r="Y186" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z186" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AA186" t="n">
         <v>0</v>
@@ -24498,7 +24498,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -24508,12 +24508,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -24622,12 +24622,12 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -24637,12 +24637,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Union Estepona CF</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Yeclano Deportivo</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -24742,7 +24742,7 @@
         <v>0</v>
       </c>
       <c r="AK188" s="3" t="n">
-        <v>45949.50694444445</v>
+        <v>45949.5</v>
       </c>
     </row>
     <row r="189">
@@ -24751,12 +24751,12 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -24766,12 +24766,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Lorient</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -24792,13 +24792,13 @@
         </is>
       </c>
       <c r="L189" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="M189" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N189" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O189" t="n">
         <v>0</v>
@@ -24831,16 +24831,16 @@
         <v>0</v>
       </c>
       <c r="Y189" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Z189" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AA189" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AB189" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AC189" t="n">
         <v>0</v>
@@ -24871,7 +24871,7 @@
         <v>0</v>
       </c>
       <c r="AK189" s="3" t="n">
-        <v>45949.51041666666</v>
+        <v>45949.50694444445</v>
       </c>
     </row>
     <row r="190">
@@ -24885,7 +24885,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -24895,12 +24895,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Metz</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="G190" t="n">
@@ -24921,49 +24921,49 @@
         </is>
       </c>
       <c r="L190" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="M190" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N190" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="O190" t="n">
+        <v>0</v>
+      </c>
+      <c r="P190" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q190" t="n">
+        <v>0</v>
+      </c>
+      <c r="R190" t="n">
+        <v>0</v>
+      </c>
+      <c r="S190" t="n">
+        <v>0</v>
+      </c>
+      <c r="T190" t="n">
+        <v>0</v>
+      </c>
+      <c r="U190" t="n">
+        <v>0</v>
+      </c>
+      <c r="V190" t="n">
+        <v>0</v>
+      </c>
+      <c r="W190" t="n">
+        <v>0</v>
+      </c>
+      <c r="X190" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y190" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Z190" t="n">
         <v>1.65</v>
-      </c>
-      <c r="M190" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="N190" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="O190" t="n">
-        <v>0</v>
-      </c>
-      <c r="P190" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q190" t="n">
-        <v>0</v>
-      </c>
-      <c r="R190" t="n">
-        <v>0</v>
-      </c>
-      <c r="S190" t="n">
-        <v>0</v>
-      </c>
-      <c r="T190" t="n">
-        <v>0</v>
-      </c>
-      <c r="U190" t="n">
-        <v>0</v>
-      </c>
-      <c r="V190" t="n">
-        <v>0</v>
-      </c>
-      <c r="W190" t="n">
-        <v>0</v>
-      </c>
-      <c r="X190" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y190" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="Z190" t="n">
-        <v>2.15</v>
       </c>
       <c r="AA190" t="n">
         <v>0</v>
@@ -25143,7 +25143,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -25153,12 +25153,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Lorient</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="G192" t="n">
@@ -25179,13 +25179,13 @@
         </is>
       </c>
       <c r="L192" t="n">
-        <v>2.95</v>
+        <v>2.35</v>
       </c>
       <c r="M192" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="N192" t="n">
-        <v>2.55</v>
+        <v>3</v>
       </c>
       <c r="O192" t="n">
         <v>0</v>
@@ -25218,16 +25218,16 @@
         <v>0</v>
       </c>
       <c r="Y192" t="n">
-        <v>2.25</v>
+        <v>1.9</v>
       </c>
       <c r="Z192" t="n">
-        <v>1.65</v>
+        <v>1.9</v>
       </c>
       <c r="AA192" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AB192" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC192" t="n">
         <v>0</v>
@@ -25267,12 +25267,12 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -25282,12 +25282,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Metz</t>
         </is>
       </c>
       <c r="G193" t="n">
@@ -25308,13 +25308,13 @@
         </is>
       </c>
       <c r="L193" t="n">
-        <v>3.75</v>
+        <v>1.65</v>
       </c>
       <c r="M193" t="n">
-        <v>3.75</v>
+        <v>3.95</v>
       </c>
       <c r="N193" t="n">
-        <v>1.93</v>
+        <v>5.1</v>
       </c>
       <c r="O193" t="n">
         <v>0</v>
@@ -25347,10 +25347,10 @@
         <v>0</v>
       </c>
       <c r="Y193" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="Z193" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AA193" t="n">
         <v>0</v>
@@ -25387,7 +25387,7 @@
         <v>0</v>
       </c>
       <c r="AK193" s="3" t="n">
-        <v>45949.52083333334</v>
+        <v>45949.51041666666</v>
       </c>
     </row>
     <row r="194">
@@ -25401,22 +25401,22 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>CD Coria</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>CF Fuenlabrada</t>
+          <t>Univ. Concepción</t>
         </is>
       </c>
       <c r="G194" t="n">
@@ -25788,7 +25788,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -25798,12 +25798,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>CD Coria</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>CF Fuenlabrada</t>
         </is>
       </c>
       <c r="G197" t="n">
@@ -25917,22 +25917,22 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>KuPS</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>HJK</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="G198" t="n">
@@ -25953,13 +25953,13 @@
         </is>
       </c>
       <c r="L198" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="M198" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="N198" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="O198" t="n">
         <v>0</v>
@@ -25992,16 +25992,16 @@
         <v>0</v>
       </c>
       <c r="Y198" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Z198" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA198" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB198" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC198" t="n">
         <v>0</v>
@@ -26175,7 +26175,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -26185,12 +26185,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="G200" t="n">
@@ -26211,13 +26211,13 @@
         </is>
       </c>
       <c r="L200" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M200" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N200" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O200" t="n">
         <v>0</v>
@@ -26250,10 +26250,10 @@
         <v>0</v>
       </c>
       <c r="Y200" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Z200" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AA200" t="n">
         <v>0</v>
@@ -26304,7 +26304,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -26314,12 +26314,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="G201" t="n">
@@ -26433,22 +26433,22 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Univ. Concepción</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="G202" t="n">
@@ -26469,13 +26469,13 @@
         </is>
       </c>
       <c r="L202" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="M202" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N202" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="O202" t="n">
         <v>0</v>
@@ -26508,10 +26508,10 @@
         <v>0</v>
       </c>
       <c r="Y202" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="Z202" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA202" t="n">
         <v>0</v>
@@ -26562,7 +26562,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -26572,12 +26572,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>KuPS</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Colo-Colo</t>
+          <t>HJK</t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -26637,10 +26637,10 @@
         <v>0</v>
       </c>
       <c r="Y203" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Z203" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AA203" t="n">
         <v>0</v>
@@ -26691,7 +26691,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -26701,12 +26701,12 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="G204" t="n">
@@ -26727,13 +26727,13 @@
         </is>
       </c>
       <c r="L204" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="M204" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="N204" t="n">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="O204" t="n">
         <v>0</v>
@@ -26766,16 +26766,16 @@
         <v>0</v>
       </c>
       <c r="Y204" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Z204" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA204" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB204" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC204" t="n">
         <v>0</v>
@@ -26820,7 +26820,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -26830,12 +26830,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="G205" t="n">
@@ -26856,13 +26856,13 @@
         </is>
       </c>
       <c r="L205" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M205" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N205" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O205" t="n">
         <v>0</v>
@@ -26895,10 +26895,10 @@
         <v>0</v>
       </c>
       <c r="Y205" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Z205" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AA205" t="n">
         <v>0</v>
@@ -26949,22 +26949,22 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Colo-Colo</t>
         </is>
       </c>
       <c r="G206" t="n">
@@ -27024,10 +27024,10 @@
         <v>0</v>
       </c>
       <c r="Y206" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z206" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AA206" t="n">
         <v>0</v>
@@ -27073,12 +27073,12 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -27088,12 +27088,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="G207" t="n">
@@ -27193,7 +27193,7 @@
         <v>0</v>
       </c>
       <c r="AK207" s="3" t="n">
-        <v>45949.54166666666</v>
+        <v>45949.52083333334</v>
       </c>
     </row>
     <row r="208">
@@ -27336,7 +27336,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -27346,12 +27346,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="G209" t="n">
@@ -27372,13 +27372,13 @@
         </is>
       </c>
       <c r="L209" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="M209" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="N209" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="O209" t="n">
         <v>0</v>
@@ -27417,10 +27417,10 @@
         <v>0</v>
       </c>
       <c r="AA209" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB209" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC209" t="n">
         <v>0</v>
@@ -27465,7 +27465,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -27475,12 +27475,12 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="G210" t="n">
@@ -27501,13 +27501,13 @@
         </is>
       </c>
       <c r="L210" t="n">
-        <v>1.37</v>
+        <v>1.97</v>
       </c>
       <c r="M210" t="n">
-        <v>4.7</v>
+        <v>3.7</v>
       </c>
       <c r="N210" t="n">
-        <v>9.5</v>
+        <v>3.65</v>
       </c>
       <c r="O210" t="n">
         <v>0</v>
@@ -27540,10 +27540,10 @@
         <v>0</v>
       </c>
       <c r="Y210" t="n">
-        <v>1.73</v>
+        <v>1.82</v>
       </c>
       <c r="Z210" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AA210" t="n">
         <v>0</v>
@@ -27594,7 +27594,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -27604,12 +27604,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="G211" t="n">
@@ -27630,13 +27630,13 @@
         </is>
       </c>
       <c r="L211" t="n">
-        <v>1.97</v>
+        <v>1.47</v>
       </c>
       <c r="M211" t="n">
-        <v>3.7</v>
+        <v>4.7</v>
       </c>
       <c r="N211" t="n">
-        <v>3.65</v>
+        <v>6.2</v>
       </c>
       <c r="O211" t="n">
         <v>0</v>
@@ -27669,16 +27669,16 @@
         <v>0</v>
       </c>
       <c r="Y211" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="Z211" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA211" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB211" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC211" t="n">
         <v>0</v>
@@ -27723,7 +27723,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -27733,12 +27733,12 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="G212" t="n">
@@ -27759,13 +27759,13 @@
         </is>
       </c>
       <c r="L212" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="M212" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="N212" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="O212" t="n">
         <v>0</v>
@@ -27798,10 +27798,10 @@
         <v>0</v>
       </c>
       <c r="Y212" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="Z212" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA212" t="n">
         <v>0</v>
@@ -27852,7 +27852,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -27862,12 +27862,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Újpest</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="G213" t="n">
@@ -27976,12 +27976,12 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -27991,12 +27991,12 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Újpest</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="G214" t="n">
@@ -28096,7 +28096,7 @@
         <v>0</v>
       </c>
       <c r="AK214" s="3" t="n">
-        <v>45949.55208333334</v>
+        <v>45949.54166666666</v>
       </c>
     </row>
     <row r="215">
@@ -28110,7 +28110,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -28120,12 +28120,12 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Real Murcia</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>UD Ibiza</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="G215" t="n">
@@ -28234,12 +28234,12 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -28249,12 +28249,12 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Real Murcia</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>UD Ibiza</t>
         </is>
       </c>
       <c r="G216" t="n">
@@ -28354,7 +28354,7 @@
         <v>0</v>
       </c>
       <c r="AK216" s="3" t="n">
-        <v>45949.5625</v>
+        <v>45949.55208333334</v>
       </c>
     </row>
     <row r="217">
@@ -28368,7 +28368,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -28378,12 +28378,12 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Akhmat Grozny</t>
         </is>
       </c>
       <c r="G217" t="n">
@@ -28404,13 +28404,13 @@
         </is>
       </c>
       <c r="L217" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="M217" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N217" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O217" t="n">
         <v>0</v>
@@ -28443,10 +28443,10 @@
         <v>0</v>
       </c>
       <c r="Y217" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Z217" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA217" t="n">
         <v>0</v>
@@ -28497,7 +28497,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -28507,12 +28507,12 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>Sint-Truiden</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Real Madrid III</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="G218" t="n">
@@ -28533,13 +28533,13 @@
         </is>
       </c>
       <c r="L218" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="M218" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N218" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O218" t="n">
         <v>0</v>
@@ -28572,10 +28572,10 @@
         <v>0</v>
       </c>
       <c r="Y218" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Z218" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AA218" t="n">
         <v>0</v>
@@ -28755,7 +28755,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -28765,12 +28765,12 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Sint-Truiden</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="G220" t="n">
@@ -28791,13 +28791,13 @@
         </is>
       </c>
       <c r="L220" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="M220" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N220" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="O220" t="n">
         <v>0</v>
@@ -28830,10 +28830,10 @@
         <v>0</v>
       </c>
       <c r="Y220" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Z220" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AA220" t="n">
         <v>0</v>
@@ -28884,7 +28884,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -28894,12 +28894,12 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Akhmat Grozny</t>
+          <t>Real Madrid III</t>
         </is>
       </c>
       <c r="G221" t="n">
@@ -28920,13 +28920,13 @@
         </is>
       </c>
       <c r="L221" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="M221" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N221" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="O221" t="n">
         <v>0</v>
@@ -28959,10 +28959,10 @@
         <v>0</v>
       </c>
       <c r="Y221" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Z221" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AA221" t="n">
         <v>0</v>
@@ -29137,27 +29137,27 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="G223" t="n">
@@ -29257,7 +29257,7 @@
         <v>0</v>
       </c>
       <c r="AK223" s="3" t="n">
-        <v>45949.58333333334</v>
+        <v>45949.5625</v>
       </c>
     </row>
     <row r="224">
@@ -29271,7 +29271,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -29281,12 +29281,12 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G224" t="n">
@@ -29307,13 +29307,13 @@
         </is>
       </c>
       <c r="L224" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="M224" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N224" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="O224" t="n">
         <v>0</v>
@@ -29346,10 +29346,10 @@
         <v>0</v>
       </c>
       <c r="Y224" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="Z224" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AA224" t="n">
         <v>0</v>
@@ -29529,22 +29529,22 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="G226" t="n">
@@ -29653,12 +29653,12 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -29668,12 +29668,12 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Zulte-Waregem</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="G227" t="n">
@@ -29694,13 +29694,13 @@
         </is>
       </c>
       <c r="L227" t="n">
-        <v>2.85</v>
+        <v>3.6</v>
       </c>
       <c r="M227" t="n">
-        <v>3.65</v>
+        <v>3.25</v>
       </c>
       <c r="N227" t="n">
-        <v>2.35</v>
+        <v>1.91</v>
       </c>
       <c r="O227" t="n">
         <v>0</v>
@@ -29733,10 +29733,10 @@
         <v>0</v>
       </c>
       <c r="Y227" t="n">
-        <v>1.65</v>
+        <v>1.99</v>
       </c>
       <c r="Z227" t="n">
-        <v>2.2</v>
+        <v>1.78</v>
       </c>
       <c r="AA227" t="n">
         <v>0</v>
@@ -29773,7 +29773,7 @@
         <v>0</v>
       </c>
       <c r="AK227" s="3" t="n">
-        <v>45949.59375</v>
+        <v>45949.58333333334</v>
       </c>
     </row>
     <row r="228">
@@ -29782,12 +29782,12 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -29797,12 +29797,12 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Zulte-Waregem</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="G228" t="n">
@@ -29823,13 +29823,13 @@
         </is>
       </c>
       <c r="L228" t="n">
-        <v>2.1</v>
+        <v>2.85</v>
       </c>
       <c r="M228" t="n">
-        <v>3.2</v>
+        <v>3.65</v>
       </c>
       <c r="N228" t="n">
-        <v>3.8</v>
+        <v>2.35</v>
       </c>
       <c r="O228" t="n">
         <v>0</v>
@@ -29862,10 +29862,10 @@
         <v>0</v>
       </c>
       <c r="Y228" t="n">
-        <v>2.4</v>
+        <v>1.65</v>
       </c>
       <c r="Z228" t="n">
-        <v>1.57</v>
+        <v>2.2</v>
       </c>
       <c r="AA228" t="n">
         <v>0</v>
@@ -29902,7 +29902,7 @@
         <v>0</v>
       </c>
       <c r="AK228" s="3" t="n">
-        <v>45949.60416666666</v>
+        <v>45949.59375</v>
       </c>
     </row>
     <row r="229">
@@ -29916,7 +29916,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -29926,12 +29926,12 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="G229" t="n">
@@ -29952,13 +29952,13 @@
         </is>
       </c>
       <c r="L229" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="M229" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N229" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O229" t="n">
         <v>0</v>
@@ -29991,10 +29991,10 @@
         <v>0</v>
       </c>
       <c r="Y229" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z229" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AA229" t="n">
         <v>0</v>
@@ -30174,7 +30174,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -30184,12 +30184,12 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="G231" t="n">
@@ -30210,13 +30210,13 @@
         </is>
       </c>
       <c r="L231" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="M231" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="N231" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="O231" t="n">
         <v>0</v>
@@ -30432,7 +30432,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -30442,12 +30442,12 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="G233" t="n">
@@ -30468,13 +30468,13 @@
         </is>
       </c>
       <c r="L233" t="n">
-        <v>2.99</v>
+        <v>2.1</v>
       </c>
       <c r="M233" t="n">
-        <v>3.58</v>
+        <v>3.2</v>
       </c>
       <c r="N233" t="n">
-        <v>2.14</v>
+        <v>3.8</v>
       </c>
       <c r="O233" t="n">
         <v>0</v>
@@ -30507,10 +30507,10 @@
         <v>0</v>
       </c>
       <c r="Y233" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Z233" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AA233" t="n">
         <v>0</v>
@@ -30556,12 +30556,12 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -30571,12 +30571,12 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="G234" t="n">
@@ -30597,13 +30597,13 @@
         </is>
       </c>
       <c r="L234" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M234" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N234" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O234" t="n">
         <v>0</v>
@@ -30636,10 +30636,10 @@
         <v>0</v>
       </c>
       <c r="Y234" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z234" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA234" t="n">
         <v>0</v>
@@ -30676,7 +30676,7 @@
         <v>0</v>
       </c>
       <c r="AK234" s="3" t="n">
-        <v>45949.625</v>
+        <v>45949.60416666666</v>
       </c>
     </row>
     <row r="235">
@@ -30819,22 +30819,22 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Universidad Católica</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="G236" t="n">
@@ -30894,10 +30894,10 @@
         <v>0</v>
       </c>
       <c r="Y236" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Z236" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AA236" t="n">
         <v>0</v>
@@ -30948,7 +30948,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -30958,12 +30958,12 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Universidad Católica</t>
         </is>
       </c>
       <c r="G237" t="n">
@@ -31023,10 +31023,10 @@
         <v>0</v>
       </c>
       <c r="Y237" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Z237" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AA237" t="n">
         <v>0</v>
@@ -31330,27 +31330,27 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Koper</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="G240" t="n">
@@ -31450,7 +31450,7 @@
         <v>0</v>
       </c>
       <c r="AK240" s="3" t="n">
-        <v>45949.63541666666</v>
+        <v>45949.625</v>
       </c>
     </row>
     <row r="241">
@@ -31459,12 +31459,12 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -31474,12 +31474,12 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Real Betis II</t>
+          <t>Koper</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Atlético Sanluqueño CF</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="G241" t="n">
@@ -31579,7 +31579,7 @@
         <v>0</v>
       </c>
       <c r="AK241" s="3" t="n">
-        <v>45949.64583333334</v>
+        <v>45949.63541666666</v>
       </c>
     </row>
     <row r="242">
@@ -31603,12 +31603,12 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Athletic Club II</t>
+          <t>Real Betis II</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>CP Cacereño</t>
+          <t>Atlético Sanluqueño CF</t>
         </is>
       </c>
       <c r="G242" t="n">
@@ -31722,7 +31722,7 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -31732,12 +31732,12 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G243" t="n">
@@ -31851,7 +31851,7 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -31861,12 +31861,12 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="G244" t="n">
@@ -31975,12 +31975,12 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -31990,12 +31990,12 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Athletic Club II</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>CP Cacereño</t>
         </is>
       </c>
       <c r="G245" t="n">
@@ -32016,13 +32016,13 @@
         </is>
       </c>
       <c r="L245" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="M245" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N245" t="n">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="O245" t="n">
         <v>0</v>
@@ -32055,10 +32055,10 @@
         <v>0</v>
       </c>
       <c r="Y245" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Z245" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AA245" t="n">
         <v>0</v>
@@ -32095,7 +32095,7 @@
         <v>0</v>
       </c>
       <c r="AK245" s="3" t="n">
-        <v>45949.65625</v>
+        <v>45949.64583333334</v>
       </c>
     </row>
     <row r="246">
@@ -32109,7 +32109,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -32119,12 +32119,12 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="G246" t="n">
@@ -32145,13 +32145,13 @@
         </is>
       </c>
       <c r="L246" t="n">
-        <v>3.65</v>
+        <v>1.55</v>
       </c>
       <c r="M246" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="N246" t="n">
-        <v>1.98</v>
+        <v>5.9</v>
       </c>
       <c r="O246" t="n">
         <v>0</v>
@@ -32184,10 +32184,10 @@
         <v>0</v>
       </c>
       <c r="Y246" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="Z246" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AA246" t="n">
         <v>0</v>
@@ -32233,27 +32233,27 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="G247" t="n">
@@ -32274,13 +32274,13 @@
         </is>
       </c>
       <c r="L247" t="n">
-        <v>1.9</v>
+        <v>3.65</v>
       </c>
       <c r="M247" t="n">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="N247" t="n">
-        <v>4.2</v>
+        <v>1.98</v>
       </c>
       <c r="O247" t="n">
         <v>0</v>
@@ -32313,10 +32313,10 @@
         <v>0</v>
       </c>
       <c r="Y247" t="n">
-        <v>2.45</v>
+        <v>1.8</v>
       </c>
       <c r="Z247" t="n">
-        <v>1.55</v>
+        <v>2</v>
       </c>
       <c r="AA247" t="n">
         <v>0</v>
@@ -32353,7 +32353,7 @@
         <v>0</v>
       </c>
       <c r="AK247" s="3" t="n">
-        <v>45949.66666666666</v>
+        <v>45949.65625</v>
       </c>
     </row>
     <row r="248">
@@ -32367,7 +32367,7 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -32377,12 +32377,12 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G248" t="n">
@@ -32496,7 +32496,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -32506,12 +32506,12 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="G249" t="n">
@@ -32625,22 +32625,22 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>Leopards</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>KCB</t>
         </is>
       </c>
       <c r="G250" t="n">
@@ -32754,22 +32754,22 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="G251" t="n">
@@ -33012,22 +33012,22 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Leopards</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>KCB</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G253" t="n">
@@ -33141,7 +33141,7 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -33151,12 +33151,12 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="G254" t="n">
@@ -33177,13 +33177,13 @@
         </is>
       </c>
       <c r="L254" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M254" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N254" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O254" t="n">
         <v>0</v>
@@ -33216,10 +33216,10 @@
         <v>0</v>
       </c>
       <c r="Y254" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Z254" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AA254" t="n">
         <v>0</v>
@@ -33394,27 +33394,27 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G256" t="n">
@@ -33514,7 +33514,7 @@
         <v>0</v>
       </c>
       <c r="AK256" s="3" t="n">
-        <v>45949.67708333334</v>
+        <v>45949.66666666666</v>
       </c>
     </row>
     <row r="257">
@@ -33523,12 +33523,12 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -33538,12 +33538,12 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="G257" t="n">
@@ -33643,7 +33643,7 @@
         <v>0</v>
       </c>
       <c r="AK257" s="3" t="n">
-        <v>45949.72916666666</v>
+        <v>45949.67708333334</v>
       </c>
     </row>
     <row r="258">
@@ -33657,22 +33657,22 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Concepción</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="G258" t="n">
@@ -33796,12 +33796,12 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G259" t="n">
@@ -33915,22 +33915,22 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="G260" t="n">
@@ -34044,22 +34044,22 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G261" t="n">
@@ -34183,12 +34183,12 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G262" t="n">
@@ -34312,12 +34312,12 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G263" t="n">
@@ -34441,12 +34441,12 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G264" t="n">
@@ -34570,12 +34570,12 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="G265" t="n">
@@ -34684,27 +34684,27 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="G266" t="n">
@@ -34725,13 +34725,13 @@
         </is>
       </c>
       <c r="L266" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="M266" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N266" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="O266" t="n">
         <v>0</v>
@@ -34804,7 +34804,7 @@
         <v>0</v>
       </c>
       <c r="AK266" s="3" t="n">
-        <v>45949.75</v>
+        <v>45949.72916666666</v>
       </c>
     </row>
     <row r="267">
@@ -34818,7 +34818,7 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
@@ -34828,12 +34828,12 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Angel City</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="G267" t="n">
@@ -34947,7 +34947,7 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
@@ -34957,12 +34957,12 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>Angel City</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="G268" t="n">
@@ -34983,13 +34983,13 @@
         </is>
       </c>
       <c r="L268" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="M268" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N268" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O268" t="n">
         <v>0</v>
@@ -35022,10 +35022,10 @@
         <v>0</v>
       </c>
       <c r="Y268" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="Z268" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AA268" t="n">
         <v>0</v>
@@ -35071,12 +35071,12 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
@@ -35086,12 +35086,12 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="G269" t="n">
@@ -35191,7 +35191,7 @@
         <v>0</v>
       </c>
       <c r="AK269" s="3" t="n">
-        <v>45949.77083333334</v>
+        <v>45949.75</v>
       </c>
     </row>
     <row r="270">
@@ -35329,12 +35329,12 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
@@ -35344,12 +35344,12 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G271" t="n">
@@ -35370,13 +35370,13 @@
         </is>
       </c>
       <c r="L271" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M271" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N271" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="O271" t="n">
         <v>0</v>
@@ -35409,10 +35409,10 @@
         <v>0</v>
       </c>
       <c r="Y271" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z271" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AA271" t="n">
         <v>0</v>
@@ -35449,7 +35449,7 @@
         <v>0</v>
       </c>
       <c r="AK271" s="3" t="n">
-        <v>45949.85416666666</v>
+        <v>45949.77083333334</v>
       </c>
     </row>
     <row r="272">
@@ -35578,6 +35578,135 @@
         <v>0</v>
       </c>
       <c r="AK272" s="3" t="n">
+        <v>45949.85416666666</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="2" t="n">
+        <v>45949</v>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>Bahia</t>
+        </is>
+      </c>
+      <c r="F273" t="inlineStr">
+        <is>
+          <t>Grêmio</t>
+        </is>
+      </c>
+      <c r="G273" t="n">
+        <v>0</v>
+      </c>
+      <c r="H273" t="n">
+        <v>0</v>
+      </c>
+      <c r="I273" t="n">
+        <v>0</v>
+      </c>
+      <c r="J273" t="n">
+        <v>0</v>
+      </c>
+      <c r="K273" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L273" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M273" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="N273" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="O273" t="n">
+        <v>0</v>
+      </c>
+      <c r="P273" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q273" t="n">
+        <v>0</v>
+      </c>
+      <c r="R273" t="n">
+        <v>0</v>
+      </c>
+      <c r="S273" t="n">
+        <v>0</v>
+      </c>
+      <c r="T273" t="n">
+        <v>0</v>
+      </c>
+      <c r="U273" t="n">
+        <v>0</v>
+      </c>
+      <c r="V273" t="n">
+        <v>0</v>
+      </c>
+      <c r="W273" t="n">
+        <v>0</v>
+      </c>
+      <c r="X273" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y273" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Z273" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AA273" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB273" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC273" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD273" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE273" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF273" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG273" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH273" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI273" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ273" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK273" s="3" t="n">
         <v>45949.85416666666</v>
       </c>
     </row>

--- a/jogos_2025-10-19.xlsx
+++ b/jogos_2025-10-19.xlsx
@@ -1572,13 +1572,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Girona II</t>
+          <t>Ibiza Islas Pitiusas</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>Valencia II</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Porreres</t>
+          <t>UD Socuéllamos</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>Rayo Majadahonda</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ourense CF</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Real Madrid II</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,13 +2217,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2256,10 +2256,10 @@
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AA14" t="n">
         <v>0</v>
@@ -2310,22 +2310,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Deportivo Alaves II</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Gernika Club</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>SD Ponferradina</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Zamora CF</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Gimnàstic de Tarragona</t>
+          <t>Monção</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>SD Tarazona</t>
+          <t>Ribeira Brava</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Monção</t>
+          <t>Linares Deportivo</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ribeira Brava</t>
+          <t>CF Lorca Deportiva</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Deportivo Alaves II</t>
+          <t>Girona II</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gernika Club</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>UD Socuéllamos</t>
+          <t>Porreres</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rayo Majadahonda</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3213,22 +3213,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,13 +3249,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3288,10 +3288,10 @@
         <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
         <v>0</v>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>SD Ponferradina</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>La Unión Atlético</t>
+          <t>Zamora CF</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>Puente Genil</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Xerez CD</t>
+          <t>Real Jaén CF</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3729,22 +3729,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Linares Deportivo</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>CF Lorca Deportiva</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,13 +3765,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>8.15</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>4.86</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>Deportivo de La Coruña W</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>Atletico Madrid W</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>CDA Navalcarnero</t>
+          <t>Real Sociedad W</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Almería II</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>UCAM Murcia CF</t>
+          <t>Xerez CD</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4245,22 +4245,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Almería II</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Real Sociedad W</t>
+          <t>UCAM Murcia CF</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Deportivo de La Coruña W</t>
+          <t>Gimnàstic de Tarragona</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Atletico Madrid W</t>
+          <t>SD Tarazona</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Ibiza Islas Pitiusas</t>
+          <t>Ourense CF</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Valencia II</t>
+          <t>Real Madrid II</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>CDA Navalcarnero</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Puente Genil</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Real Jaén CF</t>
+          <t>La Unión Atlético</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,13 +5313,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5352,10 +5352,10 @@
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Z38" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA38" t="n">
         <v>0</v>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5535,7 +5535,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,13 +5700,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5739,10 +5739,10 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="Z41" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AA41" t="n">
         <v>0</v>
@@ -5793,22 +5793,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,13 +5829,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5868,16 +5868,16 @@
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Z42" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -5922,22 +5922,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Utsikten</t>
+          <t>Hai Phong</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Trelleborg</t>
+          <t>Hoang Anh Gia Lai</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,13 +5958,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5997,10 +5997,10 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z43" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AA43" t="n">
         <v>0</v>
@@ -6051,7 +6051,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>Pho Hien</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>FLC Thanh Hoa</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6180,7 +6180,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Hai Phong</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Hoang Anh Gia Lai</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6216,13 +6216,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6255,16 +6255,16 @@
         <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z45" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AA45" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB45" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>
@@ -6309,7 +6309,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Utsikten</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Trelleborg</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6345,13 +6345,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M46" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -6384,10 +6384,10 @@
         <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z46" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA46" t="n">
         <v>0</v>
@@ -6567,7 +6567,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Rayong</t>
+          <t>Karcag SE</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Prachuap</t>
+          <t>Csákvári TK</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6603,13 +6603,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6642,10 +6642,10 @@
         <v>0</v>
       </c>
       <c r="Y48" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z48" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AA48" t="n">
         <v>0</v>
@@ -6696,7 +6696,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Csákvári TK</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Pho Hien</t>
+          <t>Rayong</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>FLC Thanh Hoa</t>
+          <t>Prachuap</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6861,13 +6861,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="M50" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6900,10 +6900,10 @@
         <v>0</v>
       </c>
       <c r="Y50" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z50" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA50" t="n">
         <v>0</v>
@@ -6990,13 +6990,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M51" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -7029,10 +7029,10 @@
         <v>0</v>
       </c>
       <c r="Y51" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Z51" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AA51" t="n">
         <v>0</v>
@@ -7083,22 +7083,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Cercle Brugge</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7119,13 +7119,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N52" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -7158,10 +7158,10 @@
         <v>0</v>
       </c>
       <c r="Y52" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Z52" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AA52" t="n">
         <v>0</v>
@@ -7212,7 +7212,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>FK Sochi</t>
+          <t>Ulm</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Zenit</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7248,13 +7248,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>10.5</v>
+        <v>2.4</v>
       </c>
       <c r="M53" t="n">
-        <v>4.7</v>
+        <v>3.6</v>
       </c>
       <c r="N53" t="n">
-        <v>1.35</v>
+        <v>2.55</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -7287,10 +7287,10 @@
         <v>0</v>
       </c>
       <c r="Y53" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Z53" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AA53" t="n">
         <v>0</v>
@@ -7341,7 +7341,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7377,13 +7377,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N54" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -7416,16 +7416,16 @@
         <v>0</v>
       </c>
       <c r="Y54" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z54" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB54" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC54" t="n">
         <v>0</v>
@@ -7470,22 +7470,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7506,13 +7506,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N55" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7545,10 +7545,10 @@
         <v>0</v>
       </c>
       <c r="Y55" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Z55" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AA55" t="n">
         <v>0</v>
@@ -7599,22 +7599,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Chonburi</t>
+          <t>Nantong Zhiyun</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Chiangrai United</t>
+          <t>Guangxi Baoyun</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7635,13 +7635,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N56" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7674,10 +7674,10 @@
         <v>0</v>
       </c>
       <c r="Y56" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z56" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AA56" t="n">
         <v>0</v>
@@ -7728,22 +7728,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Cercle Brugge</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7764,13 +7764,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="M57" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N57" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7803,10 +7803,10 @@
         <v>0</v>
       </c>
       <c r="Y57" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z57" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA57" t="n">
         <v>0</v>
@@ -7857,22 +7857,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M58" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N58" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7932,10 +7932,10 @@
         <v>0</v>
       </c>
       <c r="Y58" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Z58" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AA58" t="n">
         <v>0</v>
@@ -7986,7 +7986,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Ulm</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Magdeburg</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8022,55 +8022,55 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>2.4</v>
+        <v>1.83</v>
       </c>
       <c r="M59" t="n">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="N59" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="O59" t="n">
+        <v>0</v>
+      </c>
+      <c r="P59" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>0</v>
+      </c>
+      <c r="R59" t="n">
+        <v>0</v>
+      </c>
+      <c r="S59" t="n">
+        <v>0</v>
+      </c>
+      <c r="T59" t="n">
+        <v>0</v>
+      </c>
+      <c r="U59" t="n">
+        <v>0</v>
+      </c>
+      <c r="V59" t="n">
+        <v>0</v>
+      </c>
+      <c r="W59" t="n">
+        <v>0</v>
+      </c>
+      <c r="X59" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y59" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="Z59" t="n">
         <v>2.55</v>
       </c>
-      <c r="O59" t="n">
-        <v>0</v>
-      </c>
-      <c r="P59" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q59" t="n">
-        <v>0</v>
-      </c>
-      <c r="R59" t="n">
-        <v>0</v>
-      </c>
-      <c r="S59" t="n">
-        <v>0</v>
-      </c>
-      <c r="T59" t="n">
-        <v>0</v>
-      </c>
-      <c r="U59" t="n">
-        <v>0</v>
-      </c>
-      <c r="V59" t="n">
-        <v>0</v>
-      </c>
-      <c r="W59" t="n">
-        <v>0</v>
-      </c>
-      <c r="X59" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y59" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z59" t="n">
-        <v>0</v>
-      </c>
       <c r="AA59" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AB59" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC59" t="n">
         <v>0</v>
@@ -8115,7 +8115,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Nantong Zhiyun</t>
+          <t>Tampines Rovers</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Guangxi Baoyun</t>
+          <t>Balestier Khalsa</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8244,22 +8244,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Tampines Rovers</t>
+          <t>FK Sochi</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Balestier Khalsa</t>
+          <t>Zenit</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8280,13 +8280,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="M61" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="N61" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -8319,10 +8319,10 @@
         <v>0</v>
       </c>
       <c r="Y61" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Z61" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA61" t="n">
         <v>0</v>
@@ -8373,7 +8373,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -8383,12 +8383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Chonburi</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Chiangrai United</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8409,13 +8409,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M62" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N62" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -8448,10 +8448,10 @@
         <v>0</v>
       </c>
       <c r="Y62" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z62" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AA62" t="n">
         <v>0</v>
@@ -8512,12 +8512,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Magdeburg</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8538,10 +8538,10 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>1.83</v>
+        <v>1.65</v>
       </c>
       <c r="M63" t="n">
-        <v>3.45</v>
+        <v>4.2</v>
       </c>
       <c r="N63" t="n">
         <v>4.7</v>
@@ -8577,16 +8577,16 @@
         <v>0</v>
       </c>
       <c r="Y63" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z63" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA63" t="n">
-        <v>2.17</v>
+        <v>2.25</v>
       </c>
       <c r="AB63" t="n">
-        <v>1.7</v>
+        <v>1.53</v>
       </c>
       <c r="AC63" t="n">
         <v>0</v>
@@ -8889,22 +8889,22 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Metta - LU</t>
+          <t>Kanchanaburi</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Uthai Thani</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8925,13 +8925,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="M66" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N66" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -9028,12 +9028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Pelister</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9147,22 +9147,22 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9276,22 +9276,22 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Metta - LU</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9405,7 +9405,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9441,13 +9441,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>2.7</v>
+        <v>2.02</v>
       </c>
       <c r="M70" t="n">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="N70" t="n">
-        <v>2.55</v>
+        <v>3.55</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -9480,10 +9480,10 @@
         <v>0</v>
       </c>
       <c r="Y70" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="Z70" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AA70" t="n">
         <v>0</v>
@@ -9534,7 +9534,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>CSKA Sofia</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9570,13 +9570,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>1.48</v>
+        <v>6.4</v>
       </c>
       <c r="M71" t="n">
-        <v>3.83</v>
+        <v>3.5</v>
       </c>
       <c r="N71" t="n">
-        <v>6.76</v>
+        <v>1.52</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -9609,10 +9609,10 @@
         <v>0</v>
       </c>
       <c r="Y71" t="n">
-        <v>1.82</v>
+        <v>2.08</v>
       </c>
       <c r="Z71" t="n">
-        <v>1.94</v>
+        <v>1.64</v>
       </c>
       <c r="AA71" t="n">
         <v>0</v>
@@ -9663,7 +9663,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -9673,12 +9673,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9792,7 +9792,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9802,12 +9802,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Kanchanaburi</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Uthai Thani</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9828,13 +9828,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>1.88</v>
+        <v>3.46</v>
       </c>
       <c r="M73" t="n">
-        <v>3.45</v>
+        <v>3.63</v>
       </c>
       <c r="N73" t="n">
-        <v>3.5</v>
+        <v>1.94</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9921,7 +9921,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9931,12 +9931,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9957,13 +9957,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="M74" t="n">
-        <v>3.63</v>
+        <v>0</v>
       </c>
       <c r="N74" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -10050,7 +10050,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10179,22 +10179,22 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10215,13 +10215,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="M76" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="N76" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -10254,10 +10254,10 @@
         <v>0</v>
       </c>
       <c r="Y76" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z76" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AA76" t="n">
         <v>0</v>
@@ -10308,7 +10308,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -10318,12 +10318,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10344,13 +10344,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="M77" t="n">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="N77" t="n">
-        <v>0</v>
+        <v>6.76</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -10383,10 +10383,10 @@
         <v>0</v>
       </c>
       <c r="Y77" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="Z77" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AA77" t="n">
         <v>0</v>
@@ -10566,22 +10566,22 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10602,13 +10602,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>2.13</v>
+        <v>1.58</v>
       </c>
       <c r="M79" t="n">
-        <v>3.7</v>
+        <v>4.05</v>
       </c>
       <c r="N79" t="n">
-        <v>3.2</v>
+        <v>5.8</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -10641,10 +10641,10 @@
         <v>0</v>
       </c>
       <c r="Y79" t="n">
-        <v>1.65</v>
+        <v>1.95</v>
       </c>
       <c r="Z79" t="n">
-        <v>2.25</v>
+        <v>1.85</v>
       </c>
       <c r="AA79" t="n">
         <v>0</v>
@@ -10695,22 +10695,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10731,13 +10731,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>2.02</v>
+        <v>2.2</v>
       </c>
       <c r="M80" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="N80" t="n">
-        <v>3.55</v>
+        <v>3.2</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -10770,10 +10770,10 @@
         <v>0</v>
       </c>
       <c r="Y80" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="Z80" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AA80" t="n">
         <v>0</v>
@@ -10834,12 +10834,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10860,13 +10860,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="M81" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N81" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10953,22 +10953,22 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10989,10 +10989,10 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>2.2</v>
+        <v>2.13</v>
       </c>
       <c r="M82" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="N82" t="n">
         <v>3.2</v>
@@ -11028,10 +11028,10 @@
         <v>0</v>
       </c>
       <c r="Y82" t="n">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="Z82" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AA82" t="n">
         <v>0</v>
@@ -11082,22 +11082,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Piteå Women</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11118,13 +11118,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="M83" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N83" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -11211,7 +11211,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -11221,12 +11221,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Pelister</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11340,7 +11340,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -11350,12 +11350,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>CSKA Sofia</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11376,13 +11376,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>6.4</v>
+        <v>2.7</v>
       </c>
       <c r="M85" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="N85" t="n">
-        <v>1.52</v>
+        <v>2.55</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -11415,10 +11415,10 @@
         <v>0</v>
       </c>
       <c r="Y85" t="n">
-        <v>2.08</v>
+        <v>1.8</v>
       </c>
       <c r="Z85" t="n">
-        <v>1.64</v>
+        <v>2</v>
       </c>
       <c r="AA85" t="n">
         <v>0</v>
@@ -11598,7 +11598,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -11608,12 +11608,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Salzburg</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Rheindorf Altach</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11634,13 +11634,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="M87" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="N87" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -11673,10 +11673,10 @@
         <v>0</v>
       </c>
       <c r="Y87" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Z87" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA87" t="n">
         <v>0</v>
@@ -11727,7 +11727,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -11737,12 +11737,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Excelsior</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -11763,13 +11763,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="M88" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N88" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -11802,16 +11802,16 @@
         <v>0</v>
       </c>
       <c r="Y88" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z88" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA88" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="AB88" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC88" t="n">
         <v>0</v>
@@ -11856,7 +11856,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -11866,12 +11866,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11985,7 +11985,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11995,12 +11995,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Groningen</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Sparta Rotterdam</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12021,13 +12021,13 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M90" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N90" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -12060,16 +12060,16 @@
         <v>0</v>
       </c>
       <c r="Y90" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z90" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA90" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AB90" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC90" t="n">
         <v>0</v>
@@ -12114,7 +12114,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Excelsior</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12150,13 +12150,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="M91" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N91" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -12189,16 +12189,16 @@
         <v>0</v>
       </c>
       <c r="Y91" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z91" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA91" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AB91" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC91" t="n">
         <v>0</v>
@@ -12243,7 +12243,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -12253,12 +12253,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Blau-Weiß Linz</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12279,13 +12279,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="M92" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N92" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -12318,10 +12318,10 @@
         <v>0</v>
       </c>
       <c r="Y92" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z92" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA92" t="n">
         <v>0</v>
@@ -12759,22 +12759,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Skeid</t>
+          <t>Blau-Weiß Linz</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -12795,13 +12795,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="M96" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N96" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -12834,10 +12834,10 @@
         <v>0</v>
       </c>
       <c r="Y96" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z96" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA96" t="n">
         <v>0</v>
@@ -12888,22 +12888,22 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Groningen</t>
+          <t>Skeid</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Sparta Rotterdam</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -12924,13 +12924,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M97" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N97" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12963,16 +12963,16 @@
         <v>0</v>
       </c>
       <c r="Y97" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Z97" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA97" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="AB97" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC97" t="n">
         <v>0</v>
@@ -13017,7 +13017,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -13027,12 +13027,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Salzburg</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Rheindorf Altach</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13053,13 +13053,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>1.58</v>
+        <v>1.64</v>
       </c>
       <c r="M98" t="n">
-        <v>4.5</v>
+        <v>3.8</v>
       </c>
       <c r="N98" t="n">
-        <v>5</v>
+        <v>4.4</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -13092,10 +13092,10 @@
         <v>0</v>
       </c>
       <c r="Y98" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Z98" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AA98" t="n">
         <v>0</v>
@@ -13275,22 +13275,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Umeå</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -13311,13 +13311,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="M100" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="N100" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -13404,7 +13404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -13414,12 +13414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Ilves</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Inter Turku</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13440,13 +13440,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="M101" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="N101" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -13533,22 +13533,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Ilves</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Inter Turku</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13569,13 +13569,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="M102" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N102" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -13608,10 +13608,10 @@
         <v>0</v>
       </c>
       <c r="Y102" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Z102" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA102" t="n">
         <v>0</v>
@@ -13662,22 +13662,22 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>SJK</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -13698,13 +13698,13 @@
         </is>
       </c>
       <c r="L103" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="M103" t="n">
         <v>3.35</v>
       </c>
-      <c r="M103" t="n">
-        <v>4.05</v>
-      </c>
       <c r="N103" t="n">
-        <v>1.97</v>
+        <v>2.2</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -13737,16 +13737,16 @@
         <v>0</v>
       </c>
       <c r="Y103" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z103" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA103" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB103" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC103" t="n">
         <v>0</v>
@@ -13791,22 +13791,22 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Okzhetpes</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -13827,13 +13827,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="M104" t="n">
-        <v>3.7</v>
+        <v>3.39</v>
       </c>
       <c r="N104" t="n">
-        <v>3.15</v>
+        <v>3.43</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -13866,10 +13866,10 @@
         <v>0</v>
       </c>
       <c r="Y104" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z104" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA104" t="n">
         <v>0</v>
@@ -13920,22 +13920,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>76 Iğdır Belediyespor</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Umeå</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -13956,13 +13956,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="M105" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="N105" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -14049,7 +14049,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -14059,12 +14059,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>76 Iğdır Belediyespor</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -14085,13 +14085,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="M106" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N106" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -14124,10 +14124,10 @@
         <v>0</v>
       </c>
       <c r="Y106" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Z106" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AA106" t="n">
         <v>0</v>
@@ -14178,7 +14178,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -14188,12 +14188,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -14214,13 +14214,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="M107" t="n">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="N107" t="n">
-        <v>3.8</v>
+        <v>3.15</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -14253,10 +14253,10 @@
         <v>0</v>
       </c>
       <c r="Y107" t="n">
-        <v>2.35</v>
+        <v>1.8</v>
       </c>
       <c r="Z107" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="AA107" t="n">
         <v>0</v>
@@ -14307,7 +14307,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -14317,12 +14317,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -14343,13 +14343,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>3.25</v>
+        <v>2.02</v>
       </c>
       <c r="M108" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="N108" t="n">
-        <v>2.2</v>
+        <v>3.95</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -14382,10 +14382,10 @@
         <v>0</v>
       </c>
       <c r="Y108" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="Z108" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AA108" t="n">
         <v>0</v>
@@ -14436,22 +14436,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -14472,13 +14472,13 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="M109" t="n">
-        <v>3.48</v>
+        <v>3.85</v>
       </c>
       <c r="N109" t="n">
-        <v>3.22</v>
+        <v>3.9</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
@@ -14511,10 +14511,10 @@
         <v>0</v>
       </c>
       <c r="Y109" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Z109" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA109" t="n">
         <v>0</v>
@@ -14565,7 +14565,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -14575,12 +14575,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -14601,13 +14601,13 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="M110" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N110" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -14640,10 +14640,10 @@
         <v>0</v>
       </c>
       <c r="Y110" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Z110" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AA110" t="n">
         <v>0</v>
@@ -14694,7 +14694,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -14704,12 +14704,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Gnistan</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>SJK</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -14730,13 +14730,13 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="M111" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="N111" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="O111" t="n">
         <v>0</v>
@@ -14775,10 +14775,10 @@
         <v>0</v>
       </c>
       <c r="AA111" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB111" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC111" t="n">
         <v>0</v>
@@ -14823,22 +14823,22 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -14859,13 +14859,13 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="M112" t="n">
-        <v>3.3</v>
+        <v>3.48</v>
       </c>
       <c r="N112" t="n">
-        <v>4.3</v>
+        <v>3.22</v>
       </c>
       <c r="O112" t="n">
         <v>0</v>
@@ -14898,10 +14898,10 @@
         <v>0</v>
       </c>
       <c r="Y112" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z112" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AA112" t="n">
         <v>0</v>
@@ -14962,12 +14962,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Okzhetpes</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -14988,13 +14988,13 @@
         </is>
       </c>
       <c r="L113" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="M113" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="N113" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="O113" t="n">
         <v>0</v>
@@ -15081,22 +15081,22 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -15117,13 +15117,13 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="M114" t="n">
-        <v>3.62</v>
+        <v>3.3</v>
       </c>
       <c r="N114" t="n">
-        <v>3.23</v>
+        <v>4.3</v>
       </c>
       <c r="O114" t="n">
         <v>0</v>
@@ -15156,10 +15156,10 @@
         <v>0</v>
       </c>
       <c r="Y114" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z114" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA114" t="n">
         <v>0</v>
@@ -15633,13 +15633,13 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="M118" t="n">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="N118" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O118" t="n">
         <v>0</v>
@@ -15726,7 +15726,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -15736,12 +15736,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -15762,13 +15762,13 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="M119" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N119" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O119" t="n">
         <v>0</v>
@@ -15801,16 +15801,16 @@
         <v>0</v>
       </c>
       <c r="Y119" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z119" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AA119" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB119" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC119" t="n">
         <v>0</v>
@@ -15855,7 +15855,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -15891,13 +15891,13 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="M120" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N120" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O120" t="n">
         <v>0</v>
@@ -15930,16 +15930,16 @@
         <v>0</v>
       </c>
       <c r="Y120" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z120" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA120" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB120" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC120" t="n">
         <v>0</v>
@@ -16113,22 +16113,22 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Differdange 03</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Swift Hesperange</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -16371,7 +16371,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -16381,12 +16381,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Atert Bissen</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>UN Käerjéng</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -16500,7 +16500,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -16510,12 +16510,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Rubin Kazan</t>
+          <t>Jeunesse Canach</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Baltika</t>
+          <t>Victoria Rosport</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -16536,13 +16536,13 @@
         </is>
       </c>
       <c r="L125" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M125" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N125" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O125" t="n">
         <v>0</v>
@@ -16575,10 +16575,10 @@
         <v>0</v>
       </c>
       <c r="Y125" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Z125" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AA125" t="n">
         <v>0</v>
@@ -16629,7 +16629,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -16639,12 +16639,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>Atert Bissen</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>UN Käerjéng</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -16758,7 +16758,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -16768,12 +16768,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Hostert</t>
+          <t>Rayo Vallecano II</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>F91 Dudelange</t>
+          <t>Colonia Moscardó</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -16897,12 +16897,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Afturelding</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Vestri</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -17026,12 +17026,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -17145,22 +17145,22 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -17274,22 +17274,22 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Jeunesse Canach</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Victoria Rosport</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -17403,7 +17403,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -17413,12 +17413,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -17542,12 +17542,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -17661,22 +17661,22 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Afturelding</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Vestri</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -17790,7 +17790,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -17800,12 +17800,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -17919,22 +17919,22 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Rodange</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>UT Pétange</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -18048,7 +18048,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -18058,12 +18058,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Real Avilés</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Talavera CF</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -18177,7 +18177,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -18187,12 +18187,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Mamer</t>
+          <t>Real Avilés</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Progrès Niederkorn</t>
+          <t>Talavera CF</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -18306,7 +18306,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -18316,12 +18316,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>FCV Dender EH</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -18342,13 +18342,13 @@
         </is>
       </c>
       <c r="L139" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="M139" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N139" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="O139" t="n">
         <v>0</v>
@@ -18381,10 +18381,10 @@
         <v>0</v>
       </c>
       <c r="Y139" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z139" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AA139" t="n">
         <v>0</v>
@@ -18564,7 +18564,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -18574,12 +18574,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -18693,7 +18693,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -18703,12 +18703,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Differdange 03</t>
+          <t>Rubin Kazan</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Swift Hesperange</t>
+          <t>Baltika</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -18729,13 +18729,13 @@
         </is>
       </c>
       <c r="L142" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M142" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N142" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O142" t="n">
         <v>0</v>
@@ -18768,10 +18768,10 @@
         <v>0</v>
       </c>
       <c r="Y142" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Z142" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AA142" t="n">
         <v>0</v>
@@ -18822,7 +18822,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -18832,12 +18832,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Rodange</t>
+          <t>Gazişehir Gaziantep</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>UT Pétange</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -18951,7 +18951,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -18961,12 +18961,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Gazişehir Gaziantep</t>
+          <t>Mamer</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Progrès Niederkorn</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -19080,7 +19080,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -19090,12 +19090,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Hostert</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>F91 Dudelange</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -19209,7 +19209,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -19219,12 +19219,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Rayo Vallecano II</t>
+          <t>Jeunesse d'Esch</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Colonia Moscardó</t>
+          <t>Mondorf-les-Bains</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -19338,22 +19338,22 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Jeunesse d'Esch</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Mondorf-les-Bains</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -19467,22 +19467,22 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>FCV Dender EH</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -19503,13 +19503,13 @@
         </is>
       </c>
       <c r="L148" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="M148" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N148" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O148" t="n">
         <v>0</v>
@@ -19542,10 +19542,10 @@
         <v>0</v>
       </c>
       <c r="Y148" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z148" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA148" t="n">
         <v>0</v>
@@ -19596,22 +19596,22 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -19725,7 +19725,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -19735,12 +19735,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -19864,12 +19864,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -19983,7 +19983,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -19993,12 +19993,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -20112,7 +20112,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -20122,12 +20122,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Lausanne Sport</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -20148,13 +20148,13 @@
         </is>
       </c>
       <c r="L153" t="n">
-        <v>2.35</v>
+        <v>2.11</v>
       </c>
       <c r="M153" t="n">
-        <v>3.65</v>
+        <v>3.05</v>
       </c>
       <c r="N153" t="n">
-        <v>2.85</v>
+        <v>3.66</v>
       </c>
       <c r="O153" t="n">
         <v>0</v>
@@ -20187,10 +20187,10 @@
         <v>0</v>
       </c>
       <c r="Y153" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z153" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AA153" t="n">
         <v>0</v>
@@ -20241,7 +20241,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -20251,12 +20251,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -20280,10 +20280,10 @@
         <v>1.75</v>
       </c>
       <c r="M154" t="n">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="N154" t="n">
-        <v>4.05</v>
+        <v>5.1</v>
       </c>
       <c r="O154" t="n">
         <v>0</v>
@@ -20316,16 +20316,16 @@
         <v>0</v>
       </c>
       <c r="Y154" t="n">
-        <v>1.44</v>
+        <v>1.9</v>
       </c>
       <c r="Z154" t="n">
-        <v>2.6</v>
+        <v>1.9</v>
       </c>
       <c r="AA154" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB154" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC154" t="n">
         <v>0</v>
@@ -20370,7 +20370,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -20380,12 +20380,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>Lausanne Sport</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -20406,13 +20406,13 @@
         </is>
       </c>
       <c r="L155" t="n">
-        <v>1.75</v>
+        <v>2.35</v>
       </c>
       <c r="M155" t="n">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="N155" t="n">
-        <v>5.1</v>
+        <v>2.85</v>
       </c>
       <c r="O155" t="n">
         <v>0</v>
@@ -20445,10 +20445,10 @@
         <v>0</v>
       </c>
       <c r="Y155" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="Z155" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="AA155" t="n">
         <v>0</v>
@@ -20499,22 +20499,22 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -20535,13 +20535,13 @@
         </is>
       </c>
       <c r="L156" t="n">
-        <v>2.11</v>
+        <v>1.68</v>
       </c>
       <c r="M156" t="n">
-        <v>3.05</v>
+        <v>4.3</v>
       </c>
       <c r="N156" t="n">
-        <v>3.66</v>
+        <v>4.4</v>
       </c>
       <c r="O156" t="n">
         <v>0</v>
@@ -20574,10 +20574,10 @@
         <v>0</v>
       </c>
       <c r="Y156" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z156" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA156" t="n">
         <v>0</v>
@@ -20628,22 +20628,22 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -20664,13 +20664,13 @@
         </is>
       </c>
       <c r="L157" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="M157" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N157" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O157" t="n">
         <v>0</v>
@@ -20703,16 +20703,16 @@
         <v>0</v>
       </c>
       <c r="Y157" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z157" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AA157" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="AB157" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC157" t="n">
         <v>0</v>
@@ -20767,12 +20767,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -20793,13 +20793,13 @@
         </is>
       </c>
       <c r="L158" t="n">
-        <v>1.68</v>
+        <v>2.65</v>
       </c>
       <c r="M158" t="n">
-        <v>4.3</v>
+        <v>3.6</v>
       </c>
       <c r="N158" t="n">
-        <v>4.4</v>
+        <v>2.5</v>
       </c>
       <c r="O158" t="n">
         <v>0</v>
@@ -20832,16 +20832,16 @@
         <v>0</v>
       </c>
       <c r="Y158" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="Z158" t="n">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="AA158" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AB158" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC158" t="n">
         <v>0</v>
@@ -20886,7 +20886,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -20896,12 +20896,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Cherno More</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -20922,13 +20922,13 @@
         </is>
       </c>
       <c r="L159" t="n">
-        <v>3.69</v>
+        <v>1.75</v>
       </c>
       <c r="M159" t="n">
-        <v>3.01</v>
+        <v>4.2</v>
       </c>
       <c r="N159" t="n">
-        <v>2.11</v>
+        <v>4.05</v>
       </c>
       <c r="O159" t="n">
         <v>0</v>
@@ -20961,16 +20961,16 @@
         <v>0</v>
       </c>
       <c r="Y159" t="n">
-        <v>2.5</v>
+        <v>1.44</v>
       </c>
       <c r="Z159" t="n">
-        <v>1.5</v>
+        <v>2.6</v>
       </c>
       <c r="AA159" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB159" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC159" t="n">
         <v>0</v>
@@ -21144,7 +21144,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -21154,12 +21154,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>Cherno More</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -21180,13 +21180,13 @@
         </is>
       </c>
       <c r="L161" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="M161" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N161" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O161" t="n">
         <v>0</v>
@@ -21213,16 +21213,16 @@
         <v>0</v>
       </c>
       <c r="W161" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="X161" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Y161" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Z161" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AA161" t="n">
         <v>0</v>
@@ -21402,7 +21402,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -21412,12 +21412,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>CD Lealtad</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Deportivo La Coruña II</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -21531,7 +21531,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -21541,12 +21541,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>CD Lealtad</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña II</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -21660,7 +21660,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -21670,12 +21670,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Szentlőrinc SE</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -21789,7 +21789,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -21799,12 +21799,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -21825,13 +21825,13 @@
         </is>
       </c>
       <c r="L166" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="M166" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N166" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="O166" t="n">
         <v>0</v>
@@ -21864,10 +21864,10 @@
         <v>0</v>
       </c>
       <c r="Y166" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="Z166" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA166" t="n">
         <v>0</v>
@@ -21918,7 +21918,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -21928,12 +21928,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>Rapid Wien</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -21954,13 +21954,13 @@
         </is>
       </c>
       <c r="L167" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M167" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N167" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O167" t="n">
         <v>0</v>
@@ -21993,10 +21993,10 @@
         <v>0</v>
       </c>
       <c r="Y167" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z167" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA167" t="n">
         <v>0</v>
@@ -22047,7 +22047,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -22057,12 +22057,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Kozármisleny</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -22176,7 +22176,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -22186,12 +22186,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Beasain</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Eibar II</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -22305,7 +22305,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -22315,12 +22315,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -22434,7 +22434,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -22444,12 +22444,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>SD Ejea</t>
+          <t>Bergantiños</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>Burgos Promesas</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -22563,7 +22563,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -22573,12 +22573,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Quintanar del Rey</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -22692,7 +22692,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -22702,12 +22702,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Real Zaragoza II</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -22821,7 +22821,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -22831,12 +22831,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Szeged 2011</t>
+          <t>Rabotnički</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -22950,7 +22950,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -22960,12 +22960,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>Union Estepona CF</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Sestao River Club</t>
+          <t>Yeclano Deportivo</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -23079,7 +23079,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -23089,12 +23089,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>CD Ebro</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>UD Mutilvera</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -23115,13 +23115,13 @@
         </is>
       </c>
       <c r="L176" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="M176" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N176" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="O176" t="n">
         <v>0</v>
@@ -23154,10 +23154,10 @@
         <v>0</v>
       </c>
       <c r="Y176" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="Z176" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA176" t="n">
         <v>0</v>
@@ -23208,7 +23208,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -23218,12 +23218,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -23337,7 +23337,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -23347,12 +23347,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Sarriana</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>Szentlőrinc SE</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -23466,7 +23466,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -23476,12 +23476,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Sarriana</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -23595,7 +23595,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -23605,12 +23605,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>UD Granadilla Tenerife</t>
+          <t>CD Ebro</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Levante Las Planas</t>
+          <t>UD Mutilvera</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -23724,7 +23724,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -23734,12 +23734,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Rapid Wien</t>
+          <t>UD Granadilla Tenerife</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>Levante Las Planas</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -23760,13 +23760,13 @@
         </is>
       </c>
       <c r="L181" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M181" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N181" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="O181" t="n">
         <v>0</v>
@@ -23799,10 +23799,10 @@
         <v>0</v>
       </c>
       <c r="Y181" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z181" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AA181" t="n">
         <v>0</v>
@@ -23853,7 +23853,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -23863,12 +23863,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>Sestao River Club</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -23982,7 +23982,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -23992,12 +23992,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Rabotnički</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Makedonija GjP</t>
+          <t>Real Zaragoza II</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -24111,7 +24111,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -24121,12 +24121,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -24240,7 +24240,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -24250,12 +24250,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Bergantiños</t>
+          <t>Beasain</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Burgos Promesas</t>
+          <t>Eibar II</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -24369,7 +24369,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -24379,12 +24379,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Quintanar del Rey</t>
+          <t>Szeged 2011</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -24508,12 +24508,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>Kozármisleny</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -24627,7 +24627,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -24637,12 +24637,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Union Estepona CF</t>
+          <t>SD Ejea</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Yeclano Deportivo</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -24885,7 +24885,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -24895,12 +24895,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Rennes</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Auxerre</t>
         </is>
       </c>
       <c r="G190" t="n">
@@ -24921,13 +24921,13 @@
         </is>
       </c>
       <c r="L190" t="n">
-        <v>2.95</v>
+        <v>1.67</v>
       </c>
       <c r="M190" t="n">
-        <v>3.1</v>
+        <v>4</v>
       </c>
       <c r="N190" t="n">
-        <v>2.55</v>
+        <v>4.9</v>
       </c>
       <c r="O190" t="n">
         <v>0</v>
@@ -24960,10 +24960,10 @@
         <v>0</v>
       </c>
       <c r="Y190" t="n">
-        <v>2.25</v>
+        <v>1.78</v>
       </c>
       <c r="Z190" t="n">
-        <v>1.65</v>
+        <v>2.05</v>
       </c>
       <c r="AA190" t="n">
         <v>0</v>
@@ -25014,7 +25014,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -25024,12 +25024,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Auxerre</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="G191" t="n">
@@ -25050,13 +25050,13 @@
         </is>
       </c>
       <c r="L191" t="n">
-        <v>1.67</v>
+        <v>2.95</v>
       </c>
       <c r="M191" t="n">
-        <v>4</v>
+        <v>3.1</v>
       </c>
       <c r="N191" t="n">
-        <v>4.9</v>
+        <v>2.55</v>
       </c>
       <c r="O191" t="n">
         <v>0</v>
@@ -25089,10 +25089,10 @@
         <v>0</v>
       </c>
       <c r="Y191" t="n">
-        <v>1.78</v>
+        <v>2.25</v>
       </c>
       <c r="Z191" t="n">
-        <v>2.05</v>
+        <v>1.65</v>
       </c>
       <c r="AA191" t="n">
         <v>0</v>
@@ -25401,22 +25401,22 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Univ. Concepción</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="G194" t="n">
@@ -25530,7 +25530,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -25540,12 +25540,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="G195" t="n">
@@ -25659,7 +25659,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -25669,12 +25669,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>NK Primorje</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="G196" t="n">
@@ -25695,13 +25695,13 @@
         </is>
       </c>
       <c r="L196" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M196" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N196" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O196" t="n">
         <v>0</v>
@@ -25734,10 +25734,10 @@
         <v>0</v>
       </c>
       <c r="Y196" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Z196" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AA196" t="n">
         <v>0</v>
@@ -25917,7 +25917,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -25927,12 +25927,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="G198" t="n">
@@ -25953,13 +25953,13 @@
         </is>
       </c>
       <c r="L198" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="M198" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="N198" t="n">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="O198" t="n">
         <v>0</v>
@@ -25992,16 +25992,16 @@
         <v>0</v>
       </c>
       <c r="Y198" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Z198" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA198" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB198" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC198" t="n">
         <v>0</v>
@@ -26046,7 +26046,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -26056,12 +26056,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>NK Primorje</t>
         </is>
       </c>
       <c r="G199" t="n">
@@ -26175,7 +26175,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -26185,12 +26185,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="G200" t="n">
@@ -26211,13 +26211,13 @@
         </is>
       </c>
       <c r="L200" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M200" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N200" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O200" t="n">
         <v>0</v>
@@ -26250,10 +26250,10 @@
         <v>0</v>
       </c>
       <c r="Y200" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Z200" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AA200" t="n">
         <v>0</v>
@@ -26304,22 +26304,22 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Colo-Colo</t>
         </is>
       </c>
       <c r="G201" t="n">
@@ -26379,10 +26379,10 @@
         <v>0</v>
       </c>
       <c r="Y201" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z201" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AA201" t="n">
         <v>0</v>
@@ -26433,7 +26433,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -26443,12 +26443,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="G202" t="n">
@@ -26469,13 +26469,13 @@
         </is>
       </c>
       <c r="L202" t="n">
-        <v>3.75</v>
+        <v>1.53</v>
       </c>
       <c r="M202" t="n">
-        <v>3.75</v>
+        <v>4.4</v>
       </c>
       <c r="N202" t="n">
-        <v>1.93</v>
+        <v>5.9</v>
       </c>
       <c r="O202" t="n">
         <v>0</v>
@@ -26508,16 +26508,16 @@
         <v>0</v>
       </c>
       <c r="Y202" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="Z202" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AA202" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB202" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC202" t="n">
         <v>0</v>
@@ -26562,22 +26562,22 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>KuPS</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>HJK</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -26691,22 +26691,22 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Univ. Concepción</t>
         </is>
       </c>
       <c r="G204" t="n">
@@ -26820,22 +26820,22 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>KuPS</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>HJK</t>
         </is>
       </c>
       <c r="G205" t="n">
@@ -26949,22 +26949,22 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Colo-Colo</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="G206" t="n">
@@ -27024,10 +27024,10 @@
         <v>0</v>
       </c>
       <c r="Y206" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Z206" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AA206" t="n">
         <v>0</v>
@@ -27078,7 +27078,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -27088,12 +27088,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="G207" t="n">
@@ -27114,13 +27114,13 @@
         </is>
       </c>
       <c r="L207" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="M207" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N207" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="O207" t="n">
         <v>0</v>
@@ -27153,10 +27153,10 @@
         <v>0</v>
       </c>
       <c r="Y207" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="Z207" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA207" t="n">
         <v>0</v>
@@ -27207,7 +27207,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -27217,12 +27217,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Olympiakos</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="G208" t="n">
@@ -27243,13 +27243,13 @@
         </is>
       </c>
       <c r="L208" t="n">
-        <v>1.27</v>
+        <v>1.97</v>
       </c>
       <c r="M208" t="n">
-        <v>5.3</v>
+        <v>3.7</v>
       </c>
       <c r="N208" t="n">
-        <v>13</v>
+        <v>3.65</v>
       </c>
       <c r="O208" t="n">
         <v>0</v>
@@ -27282,10 +27282,10 @@
         <v>0</v>
       </c>
       <c r="Y208" t="n">
-        <v>1.72</v>
+        <v>1.82</v>
       </c>
       <c r="Z208" t="n">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="AA208" t="n">
         <v>0</v>
@@ -27465,7 +27465,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -27475,12 +27475,12 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Olympiakos</t>
         </is>
       </c>
       <c r="G210" t="n">
@@ -27501,13 +27501,13 @@
         </is>
       </c>
       <c r="L210" t="n">
-        <v>1.97</v>
+        <v>1.27</v>
       </c>
       <c r="M210" t="n">
-        <v>3.7</v>
+        <v>5.3</v>
       </c>
       <c r="N210" t="n">
-        <v>3.65</v>
+        <v>13</v>
       </c>
       <c r="O210" t="n">
         <v>0</v>
@@ -27540,10 +27540,10 @@
         <v>0</v>
       </c>
       <c r="Y210" t="n">
-        <v>1.82</v>
+        <v>1.72</v>
       </c>
       <c r="Z210" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="AA210" t="n">
         <v>0</v>
@@ -27594,7 +27594,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -27604,12 +27604,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="G211" t="n">
@@ -27630,13 +27630,13 @@
         </is>
       </c>
       <c r="L211" t="n">
-        <v>1.47</v>
+        <v>1.37</v>
       </c>
       <c r="M211" t="n">
         <v>4.7</v>
       </c>
       <c r="N211" t="n">
-        <v>6.2</v>
+        <v>9.5</v>
       </c>
       <c r="O211" t="n">
         <v>0</v>
@@ -27669,16 +27669,16 @@
         <v>0</v>
       </c>
       <c r="Y211" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="Z211" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA211" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB211" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC211" t="n">
         <v>0</v>
@@ -27723,7 +27723,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -27733,12 +27733,12 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="G212" t="n">
@@ -27759,13 +27759,13 @@
         </is>
       </c>
       <c r="L212" t="n">
-        <v>1.37</v>
+        <v>1.47</v>
       </c>
       <c r="M212" t="n">
         <v>4.7</v>
       </c>
       <c r="N212" t="n">
-        <v>9.5</v>
+        <v>6.2</v>
       </c>
       <c r="O212" t="n">
         <v>0</v>
@@ -27798,16 +27798,16 @@
         <v>0</v>
       </c>
       <c r="Y212" t="n">
-        <v>1.73</v>
+        <v>1.45</v>
       </c>
       <c r="Z212" t="n">
-        <v>2.1</v>
+        <v>2.55</v>
       </c>
       <c r="AA212" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB212" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC212" t="n">
         <v>0</v>
@@ -28110,7 +28110,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -28120,12 +28120,12 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Real Murcia</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>UD Ibiza</t>
         </is>
       </c>
       <c r="G215" t="n">
@@ -28239,7 +28239,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -28249,12 +28249,12 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Real Murcia</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>UD Ibiza</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="G216" t="n">
@@ -28497,7 +28497,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -28507,12 +28507,12 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Sint-Truiden</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Real Madrid III</t>
         </is>
       </c>
       <c r="G218" t="n">
@@ -28533,13 +28533,13 @@
         </is>
       </c>
       <c r="L218" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="M218" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N218" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="O218" t="n">
         <v>0</v>
@@ -28572,10 +28572,10 @@
         <v>0</v>
       </c>
       <c r="Y218" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Z218" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AA218" t="n">
         <v>0</v>
@@ -28626,7 +28626,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -28636,12 +28636,12 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="G219" t="n">
@@ -28662,13 +28662,13 @@
         </is>
       </c>
       <c r="L219" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="M219" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N219" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="O219" t="n">
         <v>0</v>
@@ -28701,16 +28701,16 @@
         <v>0</v>
       </c>
       <c r="Y219" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Z219" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA219" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AB219" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AC219" t="n">
         <v>0</v>
@@ -28755,7 +28755,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -28765,12 +28765,12 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Sint-Truiden</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="G220" t="n">
@@ -28791,13 +28791,13 @@
         </is>
       </c>
       <c r="L220" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="M220" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N220" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O220" t="n">
         <v>0</v>
@@ -28830,10 +28830,10 @@
         <v>0</v>
       </c>
       <c r="Y220" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Z220" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AA220" t="n">
         <v>0</v>
@@ -28884,7 +28884,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -28894,12 +28894,12 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Real Madrid III</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="G221" t="n">
@@ -29013,7 +29013,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -29023,12 +29023,12 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="G222" t="n">
@@ -29049,13 +29049,13 @@
         </is>
       </c>
       <c r="L222" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="M222" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N222" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="O222" t="n">
         <v>0</v>
@@ -29088,16 +29088,16 @@
         <v>0</v>
       </c>
       <c r="Y222" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z222" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA222" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AB222" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AC222" t="n">
         <v>0</v>
@@ -29142,7 +29142,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -29152,12 +29152,12 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="G223" t="n">
@@ -29271,7 +29271,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -29281,12 +29281,12 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="G224" t="n">
@@ -29400,7 +29400,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -29410,12 +29410,12 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="G225" t="n">
@@ -29436,13 +29436,13 @@
         </is>
       </c>
       <c r="L225" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="M225" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N225" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O225" t="n">
         <v>0</v>
@@ -29475,10 +29475,10 @@
         <v>0</v>
       </c>
       <c r="Y225" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Z225" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AA225" t="n">
         <v>0</v>
@@ -29658,7 +29658,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -29668,12 +29668,12 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G227" t="n">
@@ -29694,13 +29694,13 @@
         </is>
       </c>
       <c r="L227" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="M227" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N227" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="O227" t="n">
         <v>0</v>
@@ -29733,10 +29733,10 @@
         <v>0</v>
       </c>
       <c r="Y227" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="Z227" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AA227" t="n">
         <v>0</v>
@@ -29916,7 +29916,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -29926,12 +29926,12 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="G229" t="n">
@@ -30045,7 +30045,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -30055,12 +30055,12 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="G230" t="n">
@@ -30303,7 +30303,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -30313,12 +30313,12 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="G232" t="n">
@@ -30339,13 +30339,13 @@
         </is>
       </c>
       <c r="L232" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M232" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N232" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O232" t="n">
         <v>0</v>
@@ -30378,10 +30378,10 @@
         <v>0</v>
       </c>
       <c r="Y232" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z232" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA232" t="n">
         <v>0</v>
@@ -30561,7 +30561,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -30571,12 +30571,12 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="G234" t="n">
@@ -30597,13 +30597,13 @@
         </is>
       </c>
       <c r="L234" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="M234" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N234" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O234" t="n">
         <v>0</v>
@@ -30636,10 +30636,10 @@
         <v>0</v>
       </c>
       <c r="Y234" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z234" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AA234" t="n">
         <v>0</v>
@@ -30690,22 +30690,22 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>TransMara Sugar</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Bidco United</t>
+          <t>Universidad Católica</t>
         </is>
       </c>
       <c r="G235" t="n">
@@ -30765,10 +30765,10 @@
         <v>0</v>
       </c>
       <c r="Y235" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Z235" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AA235" t="n">
         <v>0</v>
@@ -30819,7 +30819,7 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -30829,12 +30829,12 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Murang'a SEAL</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Tusker</t>
         </is>
       </c>
       <c r="G236" t="n">
@@ -30948,22 +30948,22 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>TransMara Sugar</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Universidad Católica</t>
+          <t>Bidco United</t>
         </is>
       </c>
       <c r="G237" t="n">
@@ -31023,10 +31023,10 @@
         <v>0</v>
       </c>
       <c r="Y237" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Z237" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AA237" t="n">
         <v>0</v>
@@ -31077,22 +31077,22 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Murang'a SEAL</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Tusker</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="G238" t="n">
@@ -31335,22 +31335,22 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="G240" t="n">
@@ -31593,7 +31593,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -31603,12 +31603,12 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Real Betis II</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Atlético Sanluqueño CF</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G242" t="n">
@@ -31722,7 +31722,7 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -31732,12 +31732,12 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Athletic Club II</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>CP Cacereño</t>
         </is>
       </c>
       <c r="G243" t="n">
@@ -31990,12 +31990,12 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Athletic Club II</t>
+          <t>Real Betis II</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>CP Cacereño</t>
+          <t>Atlético Sanluqueño CF</t>
         </is>
       </c>
       <c r="G245" t="n">
@@ -32109,7 +32109,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -32119,12 +32119,12 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="G246" t="n">
@@ -32145,13 +32145,13 @@
         </is>
       </c>
       <c r="L246" t="n">
-        <v>1.55</v>
+        <v>3.65</v>
       </c>
       <c r="M246" t="n">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="N246" t="n">
-        <v>5.9</v>
+        <v>1.98</v>
       </c>
       <c r="O246" t="n">
         <v>0</v>
@@ -32184,10 +32184,10 @@
         <v>0</v>
       </c>
       <c r="Y246" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="Z246" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AA246" t="n">
         <v>0</v>
@@ -32238,7 +32238,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -32248,12 +32248,12 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="G247" t="n">
@@ -32274,13 +32274,13 @@
         </is>
       </c>
       <c r="L247" t="n">
-        <v>3.65</v>
+        <v>1.55</v>
       </c>
       <c r="M247" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="N247" t="n">
-        <v>1.98</v>
+        <v>5.9</v>
       </c>
       <c r="O247" t="n">
         <v>0</v>
@@ -32313,10 +32313,10 @@
         <v>0</v>
       </c>
       <c r="Y247" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="Z247" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AA247" t="n">
         <v>0</v>
@@ -32367,22 +32367,22 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="G248" t="n">
@@ -32403,13 +32403,13 @@
         </is>
       </c>
       <c r="L248" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="M248" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N248" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O248" t="n">
         <v>0</v>
@@ -32436,16 +32436,16 @@
         <v>0</v>
       </c>
       <c r="W248" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="X248" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Y248" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Z248" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AA248" t="n">
         <v>0</v>
@@ -32496,22 +32496,22 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G249" t="n">
@@ -32625,22 +32625,22 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Leopards</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>KCB</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G250" t="n">
@@ -32661,13 +32661,13 @@
         </is>
       </c>
       <c r="L250" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M250" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N250" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O250" t="n">
         <v>0</v>
@@ -32700,10 +32700,10 @@
         <v>0</v>
       </c>
       <c r="Y250" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Z250" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AA250" t="n">
         <v>0</v>
@@ -32754,7 +32754,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -32764,12 +32764,12 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="G251" t="n">
@@ -32790,13 +32790,13 @@
         </is>
       </c>
       <c r="L251" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M251" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N251" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O251" t="n">
         <v>0</v>
@@ -32829,10 +32829,10 @@
         <v>0</v>
       </c>
       <c r="Y251" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Z251" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AA251" t="n">
         <v>0</v>
@@ -32883,22 +32883,22 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G252" t="n">
@@ -32919,13 +32919,13 @@
         </is>
       </c>
       <c r="L252" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="M252" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N252" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O252" t="n">
         <v>0</v>
@@ -32952,16 +32952,16 @@
         <v>0</v>
       </c>
       <c r="W252" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="X252" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Y252" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Z252" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AA252" t="n">
         <v>0</v>
@@ -33141,22 +33141,22 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Leopards</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>KCB</t>
         </is>
       </c>
       <c r="G254" t="n">
@@ -33177,13 +33177,13 @@
         </is>
       </c>
       <c r="L254" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="M254" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N254" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O254" t="n">
         <v>0</v>
@@ -33216,10 +33216,10 @@
         <v>0</v>
       </c>
       <c r="Y254" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Z254" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AA254" t="n">
         <v>0</v>
@@ -33270,7 +33270,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -33280,12 +33280,12 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="G255" t="n">
@@ -33306,13 +33306,13 @@
         </is>
       </c>
       <c r="L255" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M255" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N255" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="O255" t="n">
         <v>0</v>
@@ -33345,10 +33345,10 @@
         <v>0</v>
       </c>
       <c r="Y255" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Z255" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AA255" t="n">
         <v>0</v>
@@ -33399,22 +33399,22 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="G256" t="n">
@@ -33657,22 +33657,22 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G258" t="n">
@@ -33796,12 +33796,12 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G259" t="n">
@@ -33915,22 +33915,22 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="G260" t="n">
@@ -34054,12 +34054,12 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G261" t="n">
@@ -34173,22 +34173,22 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Concepción</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="G262" t="n">
@@ -34312,12 +34312,12 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G263" t="n">
@@ -34441,12 +34441,12 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G264" t="n">
@@ -34570,12 +34570,12 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="G265" t="n">
@@ -34689,22 +34689,22 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="G266" t="n">
@@ -34818,7 +34818,7 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
@@ -34828,12 +34828,12 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>Angel City</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="G267" t="n">
@@ -34854,13 +34854,13 @@
         </is>
       </c>
       <c r="L267" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="M267" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N267" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O267" t="n">
         <v>0</v>
@@ -34893,10 +34893,10 @@
         <v>0</v>
       </c>
       <c r="Y267" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="Z267" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AA267" t="n">
         <v>0</v>
@@ -34957,12 +34957,12 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="G268" t="n">
@@ -34983,13 +34983,13 @@
         </is>
       </c>
       <c r="L268" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="M268" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N268" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="O268" t="n">
         <v>0</v>
@@ -35022,10 +35022,10 @@
         <v>0</v>
       </c>
       <c r="Y268" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="Z268" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AA268" t="n">
         <v>0</v>
@@ -35076,7 +35076,7 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
@@ -35086,12 +35086,12 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Angel City</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="G269" t="n">

--- a/jogos_2025-10-19.xlsx
+++ b/jogos_2025-10-19.xlsx
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -837,10 +837,10 @@
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AA3" t="n">
         <v>0</v>
@@ -1701,13 +1701,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1740,10 +1740,10 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AA10" t="n">
         <v>0</v>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ibiza Islas Pitiusas</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Valencia II</t>
+          <t>CD Alcoyano</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>UD Socuéllamos</t>
+          <t>Deportivo Alaves II</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rayo Majadahonda</t>
+          <t>Gernika Club</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>La Unión Atlético</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,13 +2217,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2256,10 +2256,10 @@
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
         <v>0</v>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Deportivo Alaves II</t>
+          <t>Monção</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gernika Club</t>
+          <t>Ribeira Brava</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>CD Alcoyano</t>
+          <t>CDA Navalcarnero</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Porreres</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Monção</t>
+          <t>Almería II</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ribeira Brava</t>
+          <t>UCAM Murcia CF</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Linares Deportivo</t>
+          <t>Gimnàstic de Tarragona</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>CF Lorca Deportiva</t>
+          <t>SD Tarazona</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2955,22 +2955,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Girona II</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Porreres</t>
+          <t>Ourense CF</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>Real Madrid II</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3213,22 +3213,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>SD Ponferradina</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Zamora CF</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3342,7 +3342,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>SD Ponferradina</t>
+          <t>Ibiza Islas Pitiusas</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Zamora CF</t>
+          <t>Valencia II</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Puente Genil</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Real Jaén CF</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,13 +3636,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3675,10 +3675,10 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AA25" t="n">
         <v>0</v>
@@ -3729,22 +3729,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>Linares Deportivo</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>CF Lorca Deportiva</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,13 +3765,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>8.15</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>4.86</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Deportivo de La Coruña W</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Atletico Madrid W</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Girona II</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Real Sociedad W</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>UD Socuéllamos</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Xerez CD</t>
+          <t>Rayo Majadahonda</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>Xerez CD</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4374,22 +4374,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Almería II</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>UCAM Murcia CF</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,13 +4410,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>8.15</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>4.86</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Gimnàstic de Tarragona</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>SD Tarazona</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Ourense CF</t>
+          <t>Deportivo de La Coruña W</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Real Madrid II</t>
+          <t>Atletico Madrid W</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>CDA Navalcarnero</t>
+          <t>Real Sociedad W</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>Puente Genil</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>La Unión Atlético</t>
+          <t>Real Jaén CF</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,13 +5313,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5352,10 +5352,10 @@
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="Z38" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AA38" t="n">
         <v>0</v>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,13 +5442,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5481,10 +5481,10 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Z39" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA39" t="n">
         <v>0</v>
@@ -5793,22 +5793,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Rayong</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Prachuap</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,13 +5829,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5868,10 +5868,10 @@
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z42" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA42" t="n">
         <v>0</v>
@@ -5922,22 +5922,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Hai Phong</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Hoang Anh Gia Lai</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6180,7 +6180,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Hai Phong</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Hoang Anh Gia Lai</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6216,13 +6216,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6255,16 +6255,16 @@
         <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Z45" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>
@@ -6309,22 +6309,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Utsikten</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Trelleborg</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6345,13 +6345,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>2.25</v>
+        <v>11.5</v>
       </c>
       <c r="M46" t="n">
-        <v>3.5</v>
+        <v>6.6</v>
       </c>
       <c r="N46" t="n">
-        <v>2.8</v>
+        <v>1.23</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -6384,16 +6384,16 @@
         <v>0</v>
       </c>
       <c r="Y46" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB46" t="n">
         <v>1.8</v>
-      </c>
-      <c r="Z46" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AA46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB46" t="n">
-        <v>0</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>
@@ -6567,22 +6567,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>Utsikten</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Csákvári TK</t>
+          <t>Trelleborg</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6603,13 +6603,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M48" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6642,10 +6642,10 @@
         <v>0</v>
       </c>
       <c r="Y48" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z48" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA48" t="n">
         <v>0</v>
@@ -6825,7 +6825,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Rayong</t>
+          <t>Karcag SE</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Prachuap</t>
+          <t>Csákvári TK</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6861,13 +6861,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N50" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6900,10 +6900,10 @@
         <v>0</v>
       </c>
       <c r="Y50" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z50" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AA50" t="n">
         <v>0</v>
@@ -7083,7 +7083,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Tampines Rovers</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Balestier Khalsa</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7212,7 +7212,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Ulm</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7248,13 +7248,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N53" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -7341,7 +7341,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Cercle Brugge</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7377,13 +7377,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="M54" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -7416,10 +7416,10 @@
         <v>0</v>
       </c>
       <c r="Y54" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z54" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA54" t="n">
         <v>0</v>
@@ -7470,7 +7470,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Nantong Zhiyun</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Guangxi Baoyun</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Nantong Zhiyun</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Guangxi Baoyun</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7728,7 +7728,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7738,12 +7738,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Cercle Brugge</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7764,13 +7764,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>3.2</v>
+        <v>2.7</v>
       </c>
       <c r="M57" t="n">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="N57" t="n">
-        <v>2.12</v>
+        <v>2.5</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7803,10 +7803,10 @@
         <v>0</v>
       </c>
       <c r="Y57" t="n">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="Z57" t="n">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="AA57" t="n">
         <v>0</v>
@@ -7857,7 +7857,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7867,12 +7867,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Chonburi</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Chiangrai United</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>2.7</v>
+        <v>1.8</v>
       </c>
       <c r="M58" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="N58" t="n">
-        <v>2.5</v>
+        <v>4.2</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7932,10 +7932,10 @@
         <v>0</v>
       </c>
       <c r="Y58" t="n">
-        <v>1.78</v>
+        <v>2</v>
       </c>
       <c r="Z58" t="n">
-        <v>2.05</v>
+        <v>1.72</v>
       </c>
       <c r="AA58" t="n">
         <v>0</v>
@@ -7996,12 +7996,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Magdeburg</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8022,10 +8022,10 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>1.83</v>
+        <v>1.65</v>
       </c>
       <c r="M59" t="n">
-        <v>3.45</v>
+        <v>4.2</v>
       </c>
       <c r="N59" t="n">
         <v>4.7</v>
@@ -8061,16 +8061,16 @@
         <v>0</v>
       </c>
       <c r="Y59" t="n">
-        <v>1.45</v>
+        <v>1.6</v>
       </c>
       <c r="Z59" t="n">
-        <v>2.55</v>
+        <v>2.35</v>
       </c>
       <c r="AA59" t="n">
-        <v>2.17</v>
+        <v>2.25</v>
       </c>
       <c r="AB59" t="n">
-        <v>1.7</v>
+        <v>1.53</v>
       </c>
       <c r="AC59" t="n">
         <v>0</v>
@@ -8115,22 +8115,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Tampines Rovers</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Balestier Khalsa</t>
+          <t>Magdeburg</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8151,13 +8151,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="M60" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N60" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -8190,16 +8190,16 @@
         <v>0</v>
       </c>
       <c r="Y60" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Z60" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AA60" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AB60" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC60" t="n">
         <v>0</v>
@@ -8373,7 +8373,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -8383,12 +8383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Chonburi</t>
+          <t>Ulm</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Chiangrai United</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8409,13 +8409,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>1.8</v>
+        <v>2.4</v>
       </c>
       <c r="M62" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="N62" t="n">
-        <v>4.2</v>
+        <v>2.55</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -8448,10 +8448,10 @@
         <v>0</v>
       </c>
       <c r="Y62" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z62" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AA62" t="n">
         <v>0</v>
@@ -8502,22 +8502,22 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8538,13 +8538,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N63" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -8577,16 +8577,16 @@
         <v>0</v>
       </c>
       <c r="Y63" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z63" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AA63" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB63" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC63" t="n">
         <v>0</v>
@@ -8925,13 +8925,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="M66" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="N66" t="n">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8964,10 +8964,10 @@
         <v>0</v>
       </c>
       <c r="Y66" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z66" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AA66" t="n">
         <v>0</v>
@@ -9147,22 +9147,22 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9276,22 +9276,22 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Metta - LU</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9312,13 +9312,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M69" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N69" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -9351,10 +9351,10 @@
         <v>0</v>
       </c>
       <c r="Y69" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z69" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA69" t="n">
         <v>0</v>
@@ -9405,22 +9405,22 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9441,13 +9441,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>2.02</v>
+        <v>2.95</v>
       </c>
       <c r="M70" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="N70" t="n">
-        <v>3.55</v>
+        <v>2.11</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -9480,10 +9480,10 @@
         <v>0</v>
       </c>
       <c r="Y70" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z70" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AA70" t="n">
         <v>0</v>
@@ -9534,22 +9534,22 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Metta - LU</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>CSKA Sofia</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9570,13 +9570,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N71" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -9609,10 +9609,10 @@
         <v>0</v>
       </c>
       <c r="Y71" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="Z71" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AA71" t="n">
         <v>0</v>
@@ -9663,7 +9663,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -9673,12 +9673,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9699,13 +9699,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="M72" t="n">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="N72" t="n">
-        <v>0</v>
+        <v>6.76</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9738,10 +9738,10 @@
         <v>0</v>
       </c>
       <c r="Y72" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="Z72" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AA72" t="n">
         <v>0</v>
@@ -9792,7 +9792,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9802,12 +9802,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>CSKA Sofia</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9828,13 +9828,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>3.46</v>
+        <v>6.4</v>
       </c>
       <c r="M73" t="n">
-        <v>3.63</v>
+        <v>3.5</v>
       </c>
       <c r="N73" t="n">
-        <v>1.94</v>
+        <v>1.52</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9867,10 +9867,10 @@
         <v>0</v>
       </c>
       <c r="Y73" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Z73" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AA73" t="n">
         <v>0</v>
@@ -9921,7 +9921,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9931,12 +9931,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9957,13 +9957,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="M74" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="N74" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -10050,7 +10050,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10086,13 +10086,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="M75" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N75" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -10125,10 +10125,10 @@
         <v>0</v>
       </c>
       <c r="Y75" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z75" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA75" t="n">
         <v>0</v>
@@ -10189,12 +10189,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10308,7 +10308,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -10318,12 +10318,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10344,13 +10344,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="M77" t="n">
-        <v>3.83</v>
+        <v>0</v>
       </c>
       <c r="N77" t="n">
-        <v>6.76</v>
+        <v>0</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -10383,10 +10383,10 @@
         <v>0</v>
       </c>
       <c r="Y77" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="Z77" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AA77" t="n">
         <v>0</v>
@@ -10437,22 +10437,22 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10473,13 +10473,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="M78" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="N78" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -10512,10 +10512,10 @@
         <v>0</v>
       </c>
       <c r="Y78" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z78" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AA78" t="n">
         <v>0</v>
@@ -10576,12 +10576,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10602,13 +10602,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>1.58</v>
+        <v>2.2</v>
       </c>
       <c r="M79" t="n">
-        <v>4.05</v>
+        <v>3.5</v>
       </c>
       <c r="N79" t="n">
-        <v>5.8</v>
+        <v>3.2</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -10641,10 +10641,10 @@
         <v>0</v>
       </c>
       <c r="Y79" t="n">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="Z79" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AA79" t="n">
         <v>0</v>
@@ -10695,22 +10695,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10731,13 +10731,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>2.2</v>
+        <v>2.02</v>
       </c>
       <c r="M80" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="N80" t="n">
-        <v>3.2</v>
+        <v>3.55</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -10770,10 +10770,10 @@
         <v>0</v>
       </c>
       <c r="Y80" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="Z80" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AA80" t="n">
         <v>0</v>
@@ -10824,22 +10824,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Piteå Women</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10860,13 +10860,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="M81" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N81" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10953,7 +10953,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10963,12 +10963,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Pelister</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10989,13 +10989,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="M82" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N82" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -11028,10 +11028,10 @@
         <v>0</v>
       </c>
       <c r="Y82" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z82" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA82" t="n">
         <v>0</v>
@@ -11092,12 +11092,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11211,7 +11211,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -11221,12 +11221,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Pelister</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11340,22 +11340,22 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11376,13 +11376,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="M85" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N85" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -11415,10 +11415,10 @@
         <v>0</v>
       </c>
       <c r="Y85" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z85" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA85" t="n">
         <v>0</v>
@@ -11598,22 +11598,22 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Salzburg</t>
+          <t>Skeid</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Rheindorf Altach</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11634,13 +11634,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="M87" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="N87" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -11673,10 +11673,10 @@
         <v>0</v>
       </c>
       <c r="Y87" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Z87" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AA87" t="n">
         <v>0</v>
@@ -11727,7 +11727,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -11737,12 +11737,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -11856,7 +11856,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -11866,12 +11866,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11985,7 +11985,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11995,12 +11995,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Groningen</t>
+          <t>Salzburg</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Sparta Rotterdam</t>
+          <t>Rheindorf Altach</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12021,13 +12021,13 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>1.95</v>
+        <v>1.58</v>
       </c>
       <c r="M90" t="n">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="N90" t="n">
-        <v>3.8</v>
+        <v>5</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -12060,16 +12060,16 @@
         <v>0</v>
       </c>
       <c r="Y90" t="n">
-        <v>1.75</v>
+        <v>1.9</v>
       </c>
       <c r="Z90" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="AA90" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="AB90" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC90" t="n">
         <v>0</v>
@@ -12114,7 +12114,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Excelsior</t>
+          <t>Blau-Weiß Linz</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12150,13 +12150,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>2.05</v>
+        <v>4.9</v>
       </c>
       <c r="M91" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="N91" t="n">
-        <v>3.3</v>
+        <v>1.73</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -12189,16 +12189,16 @@
         <v>0</v>
       </c>
       <c r="Y91" t="n">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="Z91" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AA91" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="AB91" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC91" t="n">
         <v>0</v>
@@ -12382,12 +12382,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12511,12 +12511,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12630,7 +12630,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -12640,12 +12640,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Groningen</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Sparta Rotterdam</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -12666,13 +12666,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M95" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N95" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -12705,16 +12705,16 @@
         <v>0</v>
       </c>
       <c r="Y95" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z95" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA95" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AB95" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC95" t="n">
         <v>0</v>
@@ -12759,7 +12759,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -12769,12 +12769,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Blau-Weiß Linz</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -12795,13 +12795,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>4.9</v>
+        <v>1.64</v>
       </c>
       <c r="M96" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="N96" t="n">
-        <v>1.73</v>
+        <v>4.4</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -12834,10 +12834,10 @@
         <v>0</v>
       </c>
       <c r="Y96" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z96" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA96" t="n">
         <v>0</v>
@@ -12888,22 +12888,22 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Skeid</t>
+          <t>Excelsior</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -12924,13 +12924,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="M97" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N97" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12963,16 +12963,16 @@
         <v>0</v>
       </c>
       <c r="Y97" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z97" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA97" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AB97" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC97" t="n">
         <v>0</v>
@@ -13017,7 +13017,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -13027,12 +13027,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13053,13 +13053,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="M98" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N98" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -13404,22 +13404,22 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13440,13 +13440,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="M101" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="N101" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -13533,22 +13533,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Ilves</t>
+          <t>76 Iğdır Belediyespor</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Inter Turku</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13662,7 +13662,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -13672,12 +13672,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -13698,49 +13698,49 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>3.25</v>
+        <v>1.87</v>
       </c>
       <c r="M103" t="n">
-        <v>3.35</v>
+        <v>3.85</v>
       </c>
       <c r="N103" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="O103" t="n">
+        <v>0</v>
+      </c>
+      <c r="P103" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q103" t="n">
+        <v>0</v>
+      </c>
+      <c r="R103" t="n">
+        <v>0</v>
+      </c>
+      <c r="S103" t="n">
+        <v>0</v>
+      </c>
+      <c r="T103" t="n">
+        <v>0</v>
+      </c>
+      <c r="U103" t="n">
+        <v>0</v>
+      </c>
+      <c r="V103" t="n">
+        <v>0</v>
+      </c>
+      <c r="W103" t="n">
+        <v>0</v>
+      </c>
+      <c r="X103" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y103" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="Z103" t="n">
         <v>2.2</v>
-      </c>
-      <c r="O103" t="n">
-        <v>0</v>
-      </c>
-      <c r="P103" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q103" t="n">
-        <v>0</v>
-      </c>
-      <c r="R103" t="n">
-        <v>0</v>
-      </c>
-      <c r="S103" t="n">
-        <v>0</v>
-      </c>
-      <c r="T103" t="n">
-        <v>0</v>
-      </c>
-      <c r="U103" t="n">
-        <v>0</v>
-      </c>
-      <c r="V103" t="n">
-        <v>0</v>
-      </c>
-      <c r="W103" t="n">
-        <v>0</v>
-      </c>
-      <c r="X103" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y103" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Z103" t="n">
-        <v>1.65</v>
       </c>
       <c r="AA103" t="n">
         <v>0</v>
@@ -13791,7 +13791,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -13801,12 +13801,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Gnistan</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Okzhetpes</t>
+          <t>SJK</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -13827,13 +13827,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>2.1</v>
+        <v>3.35</v>
       </c>
       <c r="M104" t="n">
-        <v>3.39</v>
+        <v>4.05</v>
       </c>
       <c r="N104" t="n">
-        <v>3.43</v>
+        <v>1.97</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -13872,10 +13872,10 @@
         <v>0</v>
       </c>
       <c r="AA104" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB104" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC104" t="n">
         <v>0</v>
@@ -13920,22 +13920,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>76 Iğdır Belediyespor</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -13956,13 +13956,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="M105" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="N105" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -14049,22 +14049,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Okzhetpes</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -14088,10 +14088,10 @@
         <v>2.1</v>
       </c>
       <c r="M106" t="n">
-        <v>3.2</v>
+        <v>3.39</v>
       </c>
       <c r="N106" t="n">
-        <v>3.8</v>
+        <v>3.43</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -14124,10 +14124,10 @@
         <v>0</v>
       </c>
       <c r="Y106" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Z106" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AA106" t="n">
         <v>0</v>
@@ -14436,7 +14436,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -14446,12 +14446,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -14472,13 +14472,13 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>1.87</v>
+        <v>3.25</v>
       </c>
       <c r="M109" t="n">
-        <v>3.85</v>
+        <v>3.35</v>
       </c>
       <c r="N109" t="n">
-        <v>3.9</v>
+        <v>2.2</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
@@ -14511,10 +14511,10 @@
         <v>0</v>
       </c>
       <c r="Y109" t="n">
-        <v>1.68</v>
+        <v>2.2</v>
       </c>
       <c r="Z109" t="n">
-        <v>2.2</v>
+        <v>1.65</v>
       </c>
       <c r="AA109" t="n">
         <v>0</v>
@@ -14565,22 +14565,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -14601,13 +14601,13 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="M110" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="N110" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -14704,12 +14704,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>Ilves</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>SJK</t>
+          <t>Inter Turku</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -14730,13 +14730,13 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="M111" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="N111" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="O111" t="n">
         <v>0</v>
@@ -14775,10 +14775,10 @@
         <v>0</v>
       </c>
       <c r="AA111" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB111" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC111" t="n">
         <v>0</v>
@@ -14823,22 +14823,22 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -14859,49 +14859,49 @@
         </is>
       </c>
       <c r="L112" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="M112" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N112" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="O112" t="n">
+        <v>0</v>
+      </c>
+      <c r="P112" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q112" t="n">
+        <v>0</v>
+      </c>
+      <c r="R112" t="n">
+        <v>0</v>
+      </c>
+      <c r="S112" t="n">
+        <v>0</v>
+      </c>
+      <c r="T112" t="n">
+        <v>0</v>
+      </c>
+      <c r="U112" t="n">
+        <v>0</v>
+      </c>
+      <c r="V112" t="n">
+        <v>0</v>
+      </c>
+      <c r="W112" t="n">
+        <v>0</v>
+      </c>
+      <c r="X112" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y112" t="n">
         <v>2</v>
       </c>
-      <c r="M112" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="N112" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="O112" t="n">
-        <v>0</v>
-      </c>
-      <c r="P112" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q112" t="n">
-        <v>0</v>
-      </c>
-      <c r="R112" t="n">
-        <v>0</v>
-      </c>
-      <c r="S112" t="n">
-        <v>0</v>
-      </c>
-      <c r="T112" t="n">
-        <v>0</v>
-      </c>
-      <c r="U112" t="n">
-        <v>0</v>
-      </c>
-      <c r="V112" t="n">
-        <v>0</v>
-      </c>
-      <c r="W112" t="n">
-        <v>0</v>
-      </c>
-      <c r="X112" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y112" t="n">
-        <v>0</v>
-      </c>
       <c r="Z112" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA112" t="n">
         <v>0</v>
@@ -14952,22 +14952,22 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -14988,13 +14988,13 @@
         </is>
       </c>
       <c r="L113" t="n">
-        <v>2.31</v>
+        <v>2.1</v>
       </c>
       <c r="M113" t="n">
-        <v>3.01</v>
+        <v>3.2</v>
       </c>
       <c r="N113" t="n">
-        <v>3.35</v>
+        <v>3.8</v>
       </c>
       <c r="O113" t="n">
         <v>0</v>
@@ -15027,10 +15027,10 @@
         <v>0</v>
       </c>
       <c r="Y113" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Z113" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AA113" t="n">
         <v>0</v>
@@ -15081,22 +15081,22 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -15117,13 +15117,13 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="M114" t="n">
-        <v>3.3</v>
+        <v>3.48</v>
       </c>
       <c r="N114" t="n">
-        <v>4.3</v>
+        <v>3.22</v>
       </c>
       <c r="O114" t="n">
         <v>0</v>
@@ -15156,10 +15156,10 @@
         <v>0</v>
       </c>
       <c r="Y114" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z114" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AA114" t="n">
         <v>0</v>
@@ -15339,7 +15339,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -15349,12 +15349,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -15468,7 +15468,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -15478,12 +15478,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -15504,13 +15504,13 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M117" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N117" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O117" t="n">
         <v>0</v>
@@ -15537,10 +15537,10 @@
         <v>0</v>
       </c>
       <c r="W117" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="X117" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Y117" t="n">
         <v>0</v>
@@ -15597,7 +15597,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -15607,12 +15607,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Zalaegerszegi TE</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Puskás</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -15633,13 +15633,13 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>2.91</v>
+        <v>2.65</v>
       </c>
       <c r="M118" t="n">
-        <v>3.47</v>
+        <v>3.65</v>
       </c>
       <c r="N118" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="O118" t="n">
         <v>0</v>
@@ -15672,16 +15672,16 @@
         <v>0</v>
       </c>
       <c r="Y118" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z118" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA118" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB118" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC118" t="n">
         <v>0</v>
@@ -15726,7 +15726,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -15736,12 +15736,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -15855,7 +15855,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>Zalaegerszegi TE</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Puskás</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -15891,13 +15891,13 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>2.65</v>
+        <v>2.91</v>
       </c>
       <c r="M120" t="n">
-        <v>3.65</v>
+        <v>3.47</v>
       </c>
       <c r="N120" t="n">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="O120" t="n">
         <v>0</v>
@@ -15930,16 +15930,16 @@
         <v>0</v>
       </c>
       <c r="Y120" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z120" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AA120" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB120" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC120" t="n">
         <v>0</v>
@@ -15984,22 +15984,22 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Hajduk Split</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -16123,12 +16123,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Differdange 03</t>
+          <t>Mamer</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Swift Hesperange</t>
+          <t>Progrès Niederkorn</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -16242,7 +16242,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -16252,12 +16252,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Suduroy</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -16371,7 +16371,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -16381,12 +16381,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -16629,22 +16629,22 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Atert Bissen</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>UN Käerjéng</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -16758,22 +16758,22 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Rayo Vallecano II</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Colonia Moscardó</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -16887,22 +16887,22 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Rubin Kazan</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Baltika</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -16923,13 +16923,13 @@
         </is>
       </c>
       <c r="L128" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M128" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N128" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O128" t="n">
         <v>0</v>
@@ -16962,10 +16962,10 @@
         <v>0</v>
       </c>
       <c r="Y128" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Z128" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AA128" t="n">
         <v>0</v>
@@ -17026,12 +17026,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -17145,22 +17145,22 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -17274,22 +17274,22 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -17403,7 +17403,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -17413,12 +17413,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -17532,7 +17532,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -17542,12 +17542,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>Afturelding</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>Vestri</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -17661,22 +17661,22 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Afturelding</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Vestri</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -17790,22 +17790,22 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>Suduroy</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -17929,12 +17929,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Rodange</t>
+          <t>Atert Bissen</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>UT Pétange</t>
+          <t>UN Käerjéng</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -18048,7 +18048,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -18058,12 +18058,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Real Avilés</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>Talavera CF</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -18177,22 +18177,22 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Real Avilés</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Talavera CF</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -18306,7 +18306,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -18316,12 +18316,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>Rodange</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>UT Pétange</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -18435,22 +18435,22 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Rayo Vallecano II</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>Colonia Moscardó</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -18564,7 +18564,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -18574,12 +18574,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>FCV Dender EH</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -18600,13 +18600,13 @@
         </is>
       </c>
       <c r="L141" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="M141" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N141" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O141" t="n">
         <v>0</v>
@@ -18639,10 +18639,10 @@
         <v>0</v>
       </c>
       <c r="Y141" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z141" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA141" t="n">
         <v>0</v>
@@ -18693,7 +18693,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -18703,12 +18703,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Rubin Kazan</t>
+          <t>Gazişehir Gaziantep</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Baltika</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -18729,13 +18729,13 @@
         </is>
       </c>
       <c r="L142" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M142" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N142" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O142" t="n">
         <v>0</v>
@@ -18768,10 +18768,10 @@
         <v>0</v>
       </c>
       <c r="Y142" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Z142" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AA142" t="n">
         <v>0</v>
@@ -18822,7 +18822,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -18832,12 +18832,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Gazişehir Gaziantep</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -18858,13 +18858,13 @@
         </is>
       </c>
       <c r="L143" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M143" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N143" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O143" t="n">
         <v>0</v>
@@ -18897,10 +18897,10 @@
         <v>0</v>
       </c>
       <c r="Y143" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z143" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AA143" t="n">
         <v>0</v>
@@ -18961,12 +18961,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Mamer</t>
+          <t>Jeunesse d'Esch</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Progrès Niederkorn</t>
+          <t>Mondorf-les-Bains</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -19090,12 +19090,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Hostert</t>
+          <t>Differdange 03</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>F91 Dudelange</t>
+          <t>Swift Hesperange</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -19209,7 +19209,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -19219,12 +19219,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Jeunesse d'Esch</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Mondorf-les-Bains</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -19338,22 +19338,22 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -19467,7 +19467,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -19477,12 +19477,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>FCV Dender EH</t>
+          <t>Hostert</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>F91 Dudelange</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -19503,13 +19503,13 @@
         </is>
       </c>
       <c r="L148" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="M148" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N148" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="O148" t="n">
         <v>0</v>
@@ -19542,10 +19542,10 @@
         <v>0</v>
       </c>
       <c r="Y148" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z148" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AA148" t="n">
         <v>0</v>
@@ -19596,22 +19596,22 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -19725,7 +19725,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -19735,12 +19735,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -19854,7 +19854,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -19864,12 +19864,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -20112,7 +20112,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -20122,12 +20122,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Cherno More</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -20148,13 +20148,13 @@
         </is>
       </c>
       <c r="L153" t="n">
-        <v>2.11</v>
+        <v>3.1</v>
       </c>
       <c r="M153" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="N153" t="n">
-        <v>3.66</v>
+        <v>2.4</v>
       </c>
       <c r="O153" t="n">
         <v>0</v>
@@ -20181,16 +20181,16 @@
         <v>0</v>
       </c>
       <c r="W153" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="X153" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Y153" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Z153" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AA153" t="n">
         <v>0</v>
@@ -20370,7 +20370,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -20380,12 +20380,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Lausanne Sport</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -20406,13 +20406,13 @@
         </is>
       </c>
       <c r="L155" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="M155" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N155" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="O155" t="n">
         <v>0</v>
@@ -20445,10 +20445,10 @@
         <v>0</v>
       </c>
       <c r="Y155" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z155" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AA155" t="n">
         <v>0</v>
@@ -20628,7 +20628,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -20638,12 +20638,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>1860 München</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -20664,13 +20664,13 @@
         </is>
       </c>
       <c r="L157" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M157" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="N157" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="O157" t="n">
         <v>0</v>
@@ -20886,7 +20886,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -20896,12 +20896,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -20922,13 +20922,13 @@
         </is>
       </c>
       <c r="L159" t="n">
-        <v>1.75</v>
+        <v>2.11</v>
       </c>
       <c r="M159" t="n">
-        <v>4.2</v>
+        <v>3.05</v>
       </c>
       <c r="N159" t="n">
-        <v>4.05</v>
+        <v>3.66</v>
       </c>
       <c r="O159" t="n">
         <v>0</v>
@@ -20961,16 +20961,16 @@
         <v>0</v>
       </c>
       <c r="Y159" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Z159" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AA159" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB159" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC159" t="n">
         <v>0</v>
@@ -21015,7 +21015,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -21025,12 +21025,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>1860 München</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -21051,13 +21051,13 @@
         </is>
       </c>
       <c r="L160" t="n">
-        <v>2.45</v>
+        <v>1.75</v>
       </c>
       <c r="M160" t="n">
-        <v>3.54</v>
+        <v>4.2</v>
       </c>
       <c r="N160" t="n">
-        <v>2.52</v>
+        <v>4.05</v>
       </c>
       <c r="O160" t="n">
         <v>0</v>
@@ -21090,16 +21090,16 @@
         <v>0</v>
       </c>
       <c r="Y160" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z160" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AA160" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB160" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC160" t="n">
         <v>0</v>
@@ -21144,7 +21144,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -21154,12 +21154,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Cherno More</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Lausanne Sport</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -21180,13 +21180,13 @@
         </is>
       </c>
       <c r="L161" t="n">
-        <v>3.1</v>
+        <v>2.35</v>
       </c>
       <c r="M161" t="n">
-        <v>3.2</v>
+        <v>3.65</v>
       </c>
       <c r="N161" t="n">
-        <v>2.4</v>
+        <v>2.85</v>
       </c>
       <c r="O161" t="n">
         <v>0</v>
@@ -21213,16 +21213,16 @@
         <v>0</v>
       </c>
       <c r="W161" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="X161" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Y161" t="n">
-        <v>2.38</v>
+        <v>1.6</v>
       </c>
       <c r="Z161" t="n">
-        <v>1.47</v>
+        <v>2.3</v>
       </c>
       <c r="AA161" t="n">
         <v>0</v>
@@ -21273,7 +21273,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -21283,12 +21283,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>CD Lealtad</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Deportivo La Coruña II</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -21309,13 +21309,13 @@
         </is>
       </c>
       <c r="L162" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="M162" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="N162" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="O162" t="n">
         <v>0</v>
@@ -21348,16 +21348,16 @@
         <v>0</v>
       </c>
       <c r="Y162" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="Z162" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AA162" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AB162" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AC162" t="n">
         <v>0</v>
@@ -21402,7 +21402,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -21412,12 +21412,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>CD Lealtad</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña II</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -21531,7 +21531,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -21541,12 +21541,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -21567,13 +21567,13 @@
         </is>
       </c>
       <c r="L164" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="M164" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="N164" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="O164" t="n">
         <v>0</v>
@@ -21606,16 +21606,16 @@
         <v>0</v>
       </c>
       <c r="Y164" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Z164" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AA164" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AB164" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AC164" t="n">
         <v>0</v>
@@ -21670,12 +21670,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>Beasain</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>Eibar II</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -21789,7 +21789,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -21799,12 +21799,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -21825,13 +21825,13 @@
         </is>
       </c>
       <c r="L166" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="M166" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N166" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="O166" t="n">
         <v>0</v>
@@ -21864,10 +21864,10 @@
         <v>0</v>
       </c>
       <c r="Y166" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="Z166" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA166" t="n">
         <v>0</v>
@@ -21918,7 +21918,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -21928,12 +21928,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Rapid Wien</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -21954,13 +21954,13 @@
         </is>
       </c>
       <c r="L167" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M167" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N167" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="O167" t="n">
         <v>0</v>
@@ -21993,10 +21993,10 @@
         <v>0</v>
       </c>
       <c r="Y167" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z167" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AA167" t="n">
         <v>0</v>
@@ -22047,7 +22047,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -22057,12 +22057,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Szeged 2011</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -22176,7 +22176,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -22186,12 +22186,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>Union Estepona CF</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Yeclano Deportivo</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -22315,12 +22315,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>Kozármisleny</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -22434,7 +22434,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -22444,12 +22444,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Bergantiños</t>
+          <t>Sarriana</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Burgos Promesas</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -22563,7 +22563,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -22573,12 +22573,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Quintanar del Rey</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -22692,7 +22692,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -22702,12 +22702,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>Szentlőrinc SE</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -22821,7 +22821,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -22831,12 +22831,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Rabotnički</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Makedonija GjP</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -22950,7 +22950,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -22960,12 +22960,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Union Estepona CF</t>
+          <t>Bergantiños</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Yeclano Deportivo</t>
+          <t>Burgos Promesas</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -23079,7 +23079,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -23089,12 +23089,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -23115,13 +23115,13 @@
         </is>
       </c>
       <c r="L176" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="M176" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N176" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="O176" t="n">
         <v>0</v>
@@ -23154,10 +23154,10 @@
         <v>0</v>
       </c>
       <c r="Y176" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="Z176" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA176" t="n">
         <v>0</v>
@@ -23208,7 +23208,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -23218,12 +23218,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>UD Granadilla Tenerife</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Levante Las Planas</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -23337,7 +23337,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -23347,12 +23347,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Szentlőrinc SE</t>
+          <t>Sestao River Club</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -23466,7 +23466,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -23476,12 +23476,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Sarriana</t>
+          <t>SD Ejea</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -23605,12 +23605,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>CD Ebro</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>UD Mutilvera</t>
+          <t>Real Zaragoza II</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -23724,7 +23724,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -23734,12 +23734,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>UD Granadilla Tenerife</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Levante Las Planas</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -23853,7 +23853,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -23863,12 +23863,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Sestao River Club</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -23982,7 +23982,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -23992,12 +23992,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Real Zaragoza II</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -24121,12 +24121,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Rabotnički</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -24240,7 +24240,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -24250,12 +24250,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Beasain</t>
+          <t>Rapid Wien</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Eibar II</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -24276,13 +24276,13 @@
         </is>
       </c>
       <c r="L185" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M185" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N185" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O185" t="n">
         <v>0</v>
@@ -24315,10 +24315,10 @@
         <v>0</v>
       </c>
       <c r="Y185" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z185" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA185" t="n">
         <v>0</v>
@@ -24369,7 +24369,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -24379,12 +24379,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Szeged 2011</t>
+          <t>CD Ebro</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>UD Mutilvera</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -24498,7 +24498,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -24508,12 +24508,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Kozármisleny</t>
+          <t>Quintanar del Rey</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -24627,7 +24627,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -24637,12 +24637,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>SD Ejea</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -24895,12 +24895,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t>Lorient</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Auxerre</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="G190" t="n">
@@ -24921,13 +24921,13 @@
         </is>
       </c>
       <c r="L190" t="n">
-        <v>1.67</v>
+        <v>2.35</v>
       </c>
       <c r="M190" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="N190" t="n">
-        <v>4.9</v>
+        <v>3</v>
       </c>
       <c r="O190" t="n">
         <v>0</v>
@@ -24960,16 +24960,16 @@
         <v>0</v>
       </c>
       <c r="Y190" t="n">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="Z190" t="n">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="AA190" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AB190" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC190" t="n">
         <v>0</v>
@@ -25014,7 +25014,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -25024,12 +25024,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Rennes</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Auxerre</t>
         </is>
       </c>
       <c r="G191" t="n">
@@ -25050,13 +25050,13 @@
         </is>
       </c>
       <c r="L191" t="n">
-        <v>2.95</v>
+        <v>1.67</v>
       </c>
       <c r="M191" t="n">
-        <v>3.1</v>
+        <v>4</v>
       </c>
       <c r="N191" t="n">
-        <v>2.55</v>
+        <v>4.9</v>
       </c>
       <c r="O191" t="n">
         <v>0</v>
@@ -25089,10 +25089,10 @@
         <v>0</v>
       </c>
       <c r="Y191" t="n">
-        <v>2.25</v>
+        <v>1.78</v>
       </c>
       <c r="Z191" t="n">
-        <v>1.65</v>
+        <v>2.05</v>
       </c>
       <c r="AA191" t="n">
         <v>0</v>
@@ -25153,12 +25153,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Lorient</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Metz</t>
         </is>
       </c>
       <c r="G192" t="n">
@@ -25179,13 +25179,13 @@
         </is>
       </c>
       <c r="L192" t="n">
-        <v>2.35</v>
+        <v>1.65</v>
       </c>
       <c r="M192" t="n">
-        <v>3.4</v>
+        <v>3.95</v>
       </c>
       <c r="N192" t="n">
-        <v>3</v>
+        <v>5.1</v>
       </c>
       <c r="O192" t="n">
         <v>0</v>
@@ -25218,16 +25218,16 @@
         <v>0</v>
       </c>
       <c r="Y192" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="Z192" t="n">
-        <v>1.9</v>
+        <v>2.15</v>
       </c>
       <c r="AA192" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AB192" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AC192" t="n">
         <v>0</v>
@@ -25272,7 +25272,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -25282,12 +25282,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Metz</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="G193" t="n">
@@ -25308,49 +25308,49 @@
         </is>
       </c>
       <c r="L193" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="M193" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N193" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="O193" t="n">
+        <v>0</v>
+      </c>
+      <c r="P193" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q193" t="n">
+        <v>0</v>
+      </c>
+      <c r="R193" t="n">
+        <v>0</v>
+      </c>
+      <c r="S193" t="n">
+        <v>0</v>
+      </c>
+      <c r="T193" t="n">
+        <v>0</v>
+      </c>
+      <c r="U193" t="n">
+        <v>0</v>
+      </c>
+      <c r="V193" t="n">
+        <v>0</v>
+      </c>
+      <c r="W193" t="n">
+        <v>0</v>
+      </c>
+      <c r="X193" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y193" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Z193" t="n">
         <v>1.65</v>
-      </c>
-      <c r="M193" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="N193" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="O193" t="n">
-        <v>0</v>
-      </c>
-      <c r="P193" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q193" t="n">
-        <v>0</v>
-      </c>
-      <c r="R193" t="n">
-        <v>0</v>
-      </c>
-      <c r="S193" t="n">
-        <v>0</v>
-      </c>
-      <c r="T193" t="n">
-        <v>0</v>
-      </c>
-      <c r="U193" t="n">
-        <v>0</v>
-      </c>
-      <c r="V193" t="n">
-        <v>0</v>
-      </c>
-      <c r="W193" t="n">
-        <v>0</v>
-      </c>
-      <c r="X193" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y193" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="Z193" t="n">
-        <v>2.15</v>
       </c>
       <c r="AA193" t="n">
         <v>0</v>
@@ -25401,7 +25401,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -25411,12 +25411,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>NK Primorje</t>
         </is>
       </c>
       <c r="G194" t="n">
@@ -25530,22 +25530,22 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Colo-Colo</t>
         </is>
       </c>
       <c r="G195" t="n">
@@ -25605,10 +25605,10 @@
         <v>0</v>
       </c>
       <c r="Y195" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z195" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AA195" t="n">
         <v>0</v>
@@ -25659,7 +25659,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -25669,12 +25669,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="G196" t="n">
@@ -25695,13 +25695,13 @@
         </is>
       </c>
       <c r="L196" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M196" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N196" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O196" t="n">
         <v>0</v>
@@ -25734,10 +25734,10 @@
         <v>0</v>
       </c>
       <c r="Y196" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Z196" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AA196" t="n">
         <v>0</v>
@@ -25788,7 +25788,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -25798,12 +25798,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>CD Coria</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>CF Fuenlabrada</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="G197" t="n">
@@ -25917,7 +25917,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -25927,12 +25927,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="G198" t="n">
@@ -25953,13 +25953,13 @@
         </is>
       </c>
       <c r="L198" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M198" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N198" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O198" t="n">
         <v>0</v>
@@ -25992,10 +25992,10 @@
         <v>0</v>
       </c>
       <c r="Y198" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Z198" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AA198" t="n">
         <v>0</v>
@@ -26046,7 +26046,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -26056,12 +26056,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>NK Primorje</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="G199" t="n">
@@ -26082,13 +26082,13 @@
         </is>
       </c>
       <c r="L199" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="M199" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="N199" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="O199" t="n">
         <v>0</v>
@@ -26121,16 +26121,16 @@
         <v>0</v>
       </c>
       <c r="Y199" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Z199" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA199" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB199" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC199" t="n">
         <v>0</v>
@@ -26175,7 +26175,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -26185,12 +26185,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="G200" t="n">
@@ -26304,22 +26304,22 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Colo-Colo</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="G201" t="n">
@@ -26379,10 +26379,10 @@
         <v>0</v>
       </c>
       <c r="Y201" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Z201" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AA201" t="n">
         <v>0</v>
@@ -26433,7 +26433,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -26443,12 +26443,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="G202" t="n">
@@ -26469,13 +26469,13 @@
         </is>
       </c>
       <c r="L202" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="M202" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="N202" t="n">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="O202" t="n">
         <v>0</v>
@@ -26508,16 +26508,16 @@
         <v>0</v>
       </c>
       <c r="Y202" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Z202" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA202" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB202" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC202" t="n">
         <v>0</v>
@@ -26562,22 +26562,22 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>KuPS</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>HJK</t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -26691,22 +26691,22 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Univ. Concepción</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="G204" t="n">
@@ -26820,22 +26820,22 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>KuPS</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>HJK</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="G205" t="n">
@@ -26856,13 +26856,13 @@
         </is>
       </c>
       <c r="L205" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="M205" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N205" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="O205" t="n">
         <v>0</v>
@@ -26895,10 +26895,10 @@
         <v>0</v>
       </c>
       <c r="Y205" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="Z205" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA205" t="n">
         <v>0</v>
@@ -26949,22 +26949,22 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Univ. Concepción</t>
         </is>
       </c>
       <c r="G206" t="n">
@@ -27078,7 +27078,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -27088,12 +27088,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>CD Coria</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>CF Fuenlabrada</t>
         </is>
       </c>
       <c r="G207" t="n">
@@ -27114,13 +27114,13 @@
         </is>
       </c>
       <c r="L207" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="M207" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N207" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="O207" t="n">
         <v>0</v>
@@ -27153,10 +27153,10 @@
         <v>0</v>
       </c>
       <c r="Y207" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="Z207" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA207" t="n">
         <v>0</v>
@@ -27207,7 +27207,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -27217,12 +27217,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Olympiakos</t>
         </is>
       </c>
       <c r="G208" t="n">
@@ -27243,13 +27243,13 @@
         </is>
       </c>
       <c r="L208" t="n">
-        <v>1.97</v>
+        <v>1.27</v>
       </c>
       <c r="M208" t="n">
-        <v>3.7</v>
+        <v>5.3</v>
       </c>
       <c r="N208" t="n">
-        <v>3.65</v>
+        <v>13</v>
       </c>
       <c r="O208" t="n">
         <v>0</v>
@@ -27282,10 +27282,10 @@
         <v>0</v>
       </c>
       <c r="Y208" t="n">
-        <v>1.82</v>
+        <v>1.72</v>
       </c>
       <c r="Z208" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="AA208" t="n">
         <v>0</v>
@@ -27336,7 +27336,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -27346,12 +27346,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="G209" t="n">
@@ -27475,12 +27475,12 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Olympiakos</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="G210" t="n">
@@ -27501,13 +27501,13 @@
         </is>
       </c>
       <c r="L210" t="n">
-        <v>1.27</v>
+        <v>1.37</v>
       </c>
       <c r="M210" t="n">
-        <v>5.3</v>
+        <v>4.7</v>
       </c>
       <c r="N210" t="n">
-        <v>13</v>
+        <v>9.5</v>
       </c>
       <c r="O210" t="n">
         <v>0</v>
@@ -27540,10 +27540,10 @@
         <v>0</v>
       </c>
       <c r="Y210" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="Z210" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="AA210" t="n">
         <v>0</v>
@@ -27594,7 +27594,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -27604,12 +27604,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="G211" t="n">
@@ -27630,13 +27630,13 @@
         </is>
       </c>
       <c r="L211" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="M211" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="N211" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="O211" t="n">
         <v>0</v>
@@ -27669,10 +27669,10 @@
         <v>0</v>
       </c>
       <c r="Y211" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="Z211" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA211" t="n">
         <v>0</v>
@@ -27852,7 +27852,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -27862,12 +27862,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="G213" t="n">
@@ -27888,13 +27888,13 @@
         </is>
       </c>
       <c r="L213" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="M213" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N213" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="O213" t="n">
         <v>0</v>
@@ -27927,10 +27927,10 @@
         <v>0</v>
       </c>
       <c r="Y213" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="Z213" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA213" t="n">
         <v>0</v>
@@ -28110,7 +28110,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -28120,12 +28120,12 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Real Murcia</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>UD Ibiza</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="G215" t="n">
@@ -28239,7 +28239,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -28249,12 +28249,12 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Real Murcia</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>UD Ibiza</t>
         </is>
       </c>
       <c r="G216" t="n">
@@ -28368,7 +28368,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -28378,12 +28378,12 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Akhmat Grozny</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="G217" t="n">
@@ -28404,13 +28404,13 @@
         </is>
       </c>
       <c r="L217" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="M217" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N217" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="O217" t="n">
         <v>0</v>
@@ -28443,10 +28443,10 @@
         <v>0</v>
       </c>
       <c r="Y217" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Z217" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AA217" t="n">
         <v>0</v>
@@ -28497,7 +28497,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -28507,12 +28507,12 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Real Madrid III</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="G218" t="n">
@@ -28533,13 +28533,13 @@
         </is>
       </c>
       <c r="L218" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="M218" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N218" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="O218" t="n">
         <v>0</v>
@@ -28572,16 +28572,16 @@
         <v>0</v>
       </c>
       <c r="Y218" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z218" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA218" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AB218" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AC218" t="n">
         <v>0</v>
@@ -28626,7 +28626,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -28636,12 +28636,12 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Real Madrid III</t>
         </is>
       </c>
       <c r="G219" t="n">
@@ -29013,7 +29013,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -29023,12 +29023,12 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="G222" t="n">
@@ -29049,13 +29049,13 @@
         </is>
       </c>
       <c r="L222" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="M222" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N222" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="O222" t="n">
         <v>0</v>
@@ -29088,16 +29088,16 @@
         <v>0</v>
       </c>
       <c r="Y222" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Z222" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA222" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AB222" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AC222" t="n">
         <v>0</v>
@@ -29142,7 +29142,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -29152,12 +29152,12 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Akhmat Grozny</t>
         </is>
       </c>
       <c r="G223" t="n">
@@ -29178,13 +29178,13 @@
         </is>
       </c>
       <c r="L223" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="M223" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N223" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O223" t="n">
         <v>0</v>
@@ -29217,10 +29217,10 @@
         <v>0</v>
       </c>
       <c r="Y223" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Z223" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA223" t="n">
         <v>0</v>
@@ -29271,7 +29271,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -29281,12 +29281,12 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="G224" t="n">
@@ -29307,13 +29307,13 @@
         </is>
       </c>
       <c r="L224" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="M224" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N224" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O224" t="n">
         <v>0</v>
@@ -29346,10 +29346,10 @@
         <v>0</v>
       </c>
       <c r="Y224" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Z224" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AA224" t="n">
         <v>0</v>
@@ -29400,22 +29400,22 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="G225" t="n">
@@ -29436,13 +29436,13 @@
         </is>
       </c>
       <c r="L225" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="M225" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N225" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O225" t="n">
         <v>0</v>
@@ -29475,10 +29475,10 @@
         <v>0</v>
       </c>
       <c r="Y225" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="Z225" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AA225" t="n">
         <v>0</v>
@@ -29529,22 +29529,22 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="G226" t="n">
@@ -29694,13 +29694,13 @@
         </is>
       </c>
       <c r="L227" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="M227" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N227" t="n">
-        <v>0</v>
+        <v>6.04</v>
       </c>
       <c r="O227" t="n">
         <v>0</v>
@@ -29916,7 +29916,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -29926,12 +29926,12 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="G229" t="n">
@@ -29952,13 +29952,13 @@
         </is>
       </c>
       <c r="L229" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="M229" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="N229" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="O229" t="n">
         <v>0</v>
@@ -30055,12 +30055,12 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="G230" t="n">
@@ -30174,7 +30174,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -30184,12 +30184,12 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="G231" t="n">
@@ -30210,13 +30210,13 @@
         </is>
       </c>
       <c r="L231" t="n">
-        <v>2.99</v>
+        <v>2.75</v>
       </c>
       <c r="M231" t="n">
-        <v>3.58</v>
+        <v>3.15</v>
       </c>
       <c r="N231" t="n">
-        <v>2.14</v>
+        <v>2.7</v>
       </c>
       <c r="O231" t="n">
         <v>0</v>
@@ -30249,10 +30249,10 @@
         <v>0</v>
       </c>
       <c r="Y231" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z231" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA231" t="n">
         <v>0</v>
@@ -30303,7 +30303,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -30313,12 +30313,12 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="G232" t="n">
@@ -30339,13 +30339,13 @@
         </is>
       </c>
       <c r="L232" t="n">
-        <v>2.75</v>
+        <v>2.1</v>
       </c>
       <c r="M232" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="N232" t="n">
-        <v>2.7</v>
+        <v>3.8</v>
       </c>
       <c r="O232" t="n">
         <v>0</v>
@@ -30378,10 +30378,10 @@
         <v>0</v>
       </c>
       <c r="Y232" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="Z232" t="n">
-        <v>1.8</v>
+        <v>1.57</v>
       </c>
       <c r="AA232" t="n">
         <v>0</v>
@@ -30432,7 +30432,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -30442,12 +30442,12 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="G233" t="n">
@@ -30468,13 +30468,13 @@
         </is>
       </c>
       <c r="L233" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="M233" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N233" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="O233" t="n">
         <v>0</v>
@@ -30507,10 +30507,10 @@
         <v>0</v>
       </c>
       <c r="Y233" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Z233" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AA233" t="n">
         <v>0</v>
@@ -30561,7 +30561,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -30571,12 +30571,12 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="G234" t="n">
@@ -30690,7 +30690,7 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -30700,12 +30700,12 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Universidad Católica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="G235" t="n">
@@ -30765,10 +30765,10 @@
         <v>0</v>
       </c>
       <c r="Y235" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Z235" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AA235" t="n">
         <v>0</v>
@@ -30829,12 +30829,12 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Murang'a SEAL</t>
+          <t>TransMara Sugar</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Tusker</t>
+          <t>Bidco United</t>
         </is>
       </c>
       <c r="G236" t="n">
@@ -30948,7 +30948,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -30958,12 +30958,12 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>TransMara Sugar</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Bidco United</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="G237" t="n">
@@ -30984,13 +30984,13 @@
         </is>
       </c>
       <c r="L237" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M237" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N237" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O237" t="n">
         <v>0</v>
@@ -31023,10 +31023,10 @@
         <v>0</v>
       </c>
       <c r="Y237" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Z237" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AA237" t="n">
         <v>0</v>
@@ -31077,7 +31077,7 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -31087,12 +31087,12 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Universidad Católica</t>
         </is>
       </c>
       <c r="G238" t="n">
@@ -31152,10 +31152,10 @@
         <v>0</v>
       </c>
       <c r="Y238" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Z238" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AA238" t="n">
         <v>0</v>
@@ -31206,7 +31206,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -31216,12 +31216,12 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>PAOK</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="G239" t="n">
@@ -31242,13 +31242,13 @@
         </is>
       </c>
       <c r="L239" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M239" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N239" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="O239" t="n">
         <v>0</v>
@@ -31281,10 +31281,10 @@
         <v>0</v>
       </c>
       <c r="Y239" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="Z239" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AA239" t="n">
         <v>0</v>
@@ -31335,7 +31335,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -31345,12 +31345,12 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Murang'a SEAL</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Tusker</t>
         </is>
       </c>
       <c r="G240" t="n">
@@ -31593,7 +31593,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -31603,12 +31603,12 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Real Betis II</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Atlético Sanluqueño CF</t>
         </is>
       </c>
       <c r="G242" t="n">
@@ -31722,7 +31722,7 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -31732,12 +31732,12 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Athletic Club II</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>CP Cacereño</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G243" t="n">
@@ -31990,12 +31990,12 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Real Betis II</t>
+          <t>Athletic Club II</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Atlético Sanluqueño CF</t>
+          <t>CP Cacereño</t>
         </is>
       </c>
       <c r="G245" t="n">
@@ -32496,22 +32496,22 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G249" t="n">
@@ -32532,13 +32532,13 @@
         </is>
       </c>
       <c r="L249" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M249" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N249" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O249" t="n">
         <v>0</v>
@@ -32571,10 +32571,10 @@
         <v>0</v>
       </c>
       <c r="Y249" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Z249" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AA249" t="n">
         <v>0</v>
@@ -32625,22 +32625,22 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G250" t="n">
@@ -32661,13 +32661,13 @@
         </is>
       </c>
       <c r="L250" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M250" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N250" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="O250" t="n">
         <v>0</v>
@@ -32700,10 +32700,10 @@
         <v>0</v>
       </c>
       <c r="Y250" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Z250" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AA250" t="n">
         <v>0</v>
@@ -32754,22 +32754,22 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G251" t="n">
@@ -32790,13 +32790,13 @@
         </is>
       </c>
       <c r="L251" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="M251" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N251" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O251" t="n">
         <v>0</v>
@@ -32829,10 +32829,10 @@
         <v>0</v>
       </c>
       <c r="Y251" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Z251" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AA251" t="n">
         <v>0</v>
@@ -32883,22 +32883,22 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="G252" t="n">
@@ -32919,13 +32919,13 @@
         </is>
       </c>
       <c r="L252" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M252" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N252" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O252" t="n">
         <v>0</v>
@@ -32958,10 +32958,10 @@
         <v>0</v>
       </c>
       <c r="Y252" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Z252" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AA252" t="n">
         <v>0</v>
@@ -33012,22 +33012,22 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Leopards</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>KCB</t>
         </is>
       </c>
       <c r="G253" t="n">
@@ -33141,22 +33141,22 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Leopards</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>KCB</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="G254" t="n">
@@ -33270,7 +33270,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -33280,12 +33280,12 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="G255" t="n">
@@ -33409,12 +33409,12 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G256" t="n">
@@ -33657,22 +33657,22 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="G258" t="n">
@@ -33796,12 +33796,12 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G259" t="n">
@@ -33925,12 +33925,12 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G260" t="n">
@@ -34054,12 +34054,12 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G261" t="n">
@@ -34173,22 +34173,22 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="G262" t="n">
@@ -34312,12 +34312,12 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="G263" t="n">
@@ -34431,22 +34431,22 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Concepción</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="G264" t="n">
@@ -34570,12 +34570,12 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G265" t="n">
@@ -34689,22 +34689,22 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G266" t="n">
@@ -34818,7 +34818,7 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
@@ -34828,12 +34828,12 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>Angel City</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="G267" t="n">
@@ -34854,13 +34854,13 @@
         </is>
       </c>
       <c r="L267" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="M267" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N267" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="O267" t="n">
         <v>0</v>
@@ -34893,10 +34893,10 @@
         <v>0</v>
       </c>
       <c r="Y267" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="Z267" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AA267" t="n">
         <v>0</v>
@@ -35076,7 +35076,7 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
@@ -35086,12 +35086,12 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>Angel City</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="G269" t="n">
@@ -35112,13 +35112,13 @@
         </is>
       </c>
       <c r="L269" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="M269" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N269" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O269" t="n">
         <v>0</v>
@@ -35151,10 +35151,10 @@
         <v>0</v>
       </c>
       <c r="Y269" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="Z269" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AA269" t="n">
         <v>0</v>
@@ -35215,12 +35215,12 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G270" t="n">
@@ -35344,12 +35344,12 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G271" t="n">
